--- a/Catalogo_Maestro.xlsx
+++ b/Catalogo_Maestro.xlsx
@@ -9,20 +9,21 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PixelArt_TODO" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personajes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPCs_Clientes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edificios" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiles_Suelo" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiles_Pared" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Icons" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recetas" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investigaciones" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedidos_Tipos" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progresion" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eventos" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModoCompañero" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guia_Estilo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personajes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPCs_Clientes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edificios" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiles_Suelo" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiles_Pared" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Icons" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recetas" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investigaciones" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedidos_Tipos" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progresion" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eventos" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModoCompañero" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +75,10 @@
     <font>
       <i val="1"/>
       <color rgb="00888888"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="16">
@@ -190,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -251,6 +256,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1044,7 +1053,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
         <is>
@@ -1058,6 +1066,2010 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Tamaño</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Filename sugerido</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Color/Tema</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Función</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>Animación</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Descripción Sprite</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>icon_coin</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Icono Moneda</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_coin.png</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Oro brillante</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Indica coins en HUD.</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="17" t="inlineStr">
+        <is>
+          <t>Spin 6f loop (rotación) · idle alterna estática + spin cada 4s</t>
+        </is>
+      </c>
+      <c r="K2" s="16" t="inlineStr">
+        <is>
+          <t>Moneda dorada con símbolo grabado y brillo (HUD monedas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>icon_reputation</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Icono Reputación</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_reputation.png</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Estrella dorada</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Indica reputación.</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K3" s="16" t="inlineStr">
+        <is>
+          <t>Estrella dorada de 4 puntas con destellos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>icon_inventory</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Icono Inventario</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_inventory.png</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Mochila marrón</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Botón inventario.</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
+        <is>
+          <t>Mochila marrón con bolsillo dorado y correas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>icon_build</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Icono Construir</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_build.png</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Martillo dorado</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Botón construir.</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>Muro de ladrillos terracota con techito dorado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>icon_research</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Icono Investigación</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_research.png</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Libro abierto azul</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Botón investigación.</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t>Lupa dorada con lente cyan y mango.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>icon_shop</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Icono Tienda</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_shop.png</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Bolsa con monedas</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Botón tienda.</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>Tiendita con toldo rojo/crema y puerta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>icon_orders</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Icono Pedidos</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_orders.png</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Pergamino con marca</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Botón pedidos.</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t>Portapapeles crema con clip, líneas y checks verdes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>icon_settings</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Icono Ajustes</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_settings.png</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Engranaje plateado</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Botón ajustes.</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>Engranaje gris con centro hueco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>icon_companion</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Icono Compañero</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_companion.png</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Silueta mago miniatura</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Botón modo compañero.</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>Huellita de pata lila con destello.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>icon_pomodoro</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Icono Pomodoro</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Compañero</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_pomodoro.png</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Tomate rojo con tallo</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Widget pomodoro.</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>Spin 6f loop (rotación) · idle alterna estática + spin cada 4s</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>Tomate rojo con hojitas y manecillas de reloj.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>icon_notes</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Icono Notas</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Compañero</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_notes.png</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Pergamino con pluma</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Widget notas.</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>Libreta crema con margen rojo y lápiz dorado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>icon_todo</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Icono Tareas</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Compañero</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_todo.png</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Lista con check verde</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Widget to-do.</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
+        <is>
+          <t>Lista con 3 casillas (2 con check verde).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>icon_ambient</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Icono Ambiente</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Compañero</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_ambient.png</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Onda de sonido azul</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Widget mezclador ambient.</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
+          <t>Hoja zen verde con ondas de sonido cyan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>icon_music</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Icono Música</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Compañero</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_music.png</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Nota musical dorada</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Widget reproductor.</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K15" s="16" t="inlineStr">
+        <is>
+          <t>Doble corchea blanca con notas lila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>icon_save</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Icono Guardar</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_save.png</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Disquete azul</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Botón guardar.</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>Disquete azul con etiqueta cyan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>icon_load</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Icono Cargar</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_load.png</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Carpeta abierta dorada</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Botón cargar.</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K17" s="16" t="inlineStr">
+        <is>
+          <t>Carpeta dorada con flecha blanca de salida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>icon_close</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Icono Cerrar</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_close.png</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>X roja simple</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Cerrar panel.</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K18" s="16" t="inlineStr">
+        <is>
+          <t>Círculo rojo con X blanca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>icon_help</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Icono Ayuda</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_help.png</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Interrogación azul</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Tooltip ayuda.</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
+          <t>Círculo azul con interrogación blanca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>icon_check</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Icono Check</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_check.png</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Tick verde</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Confirmar.</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" s="16" t="inlineStr">
+        <is>
+          <t>Círculo verde con check blanco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>icon_alert</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Icono Alerta</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_alert.png</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Triángulo amarillo !</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Notificación.</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>Triángulo dorado con exclamación oscura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>icon_upgrade</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Icono Mejora</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_upgrade.png</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Flecha arriba dorada</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Botón mejorar.</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" s="16" t="inlineStr">
+        <is>
+          <t>Flecha verde gruesa hacia arriba con destellos dorados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>icon_craft</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Icono Craftear</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/icon_craft.png</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Yunque pequeño</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Botón craftear.</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" s="16" t="inlineStr">
+        <is>
+          <t>Martillo y llave inglesa cruzados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>cursor_default</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Cursor Default</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/cursor_default.png</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Flecha negra con borde</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Cursor normal.</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K24" s="16" t="inlineStr">
+        <is>
+          <t>Flecha blanca con borde oscuro y detalle lila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>cursor_build</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Cursor Construir</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/cursor_build.png</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Martillo pequeño</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Cursor modo construcción.</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>Martillito plateado con mango de madera y chispas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>cursor_collect</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Cursor Recolectar</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/cursor_collect.png</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Mano abierta</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Hover sobre recurso.</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" s="16" t="inlineStr">
+        <is>
+          <t>Manita agarrando con dedos separados y brillitos dorados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>frame_panel</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Frame Panel</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>9-slice</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/frame_panel.png</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Madera con borde dorado</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Marco de panel general.</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>9-slice</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" s="16" t="inlineStr">
+        <is>
+          <t>Marco 9-slice violeta con borde dorado y esquinas brillantes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>frame_popup</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Frame Popup</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>9-slice</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/frame_popup.png</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Cristal con borde brillante</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Marco de popups.</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>9-slice</t>
+        </is>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" s="16" t="inlineStr">
+        <is>
+          <t>Marco violeta claro con doble borde dorado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>frame_tooltip</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Frame Tooltip</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>9-slice</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/frame_tooltip.png</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Marrón oscuro con borde</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Marco tooltips.</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>9-slice</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" s="16" t="inlineStr">
+        <is>
+          <t>Marco oscuro translúcido con borde lila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>button_default</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Botón Default</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>32×32 / 9-slice</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/button_default.png</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Madera con dorado</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Estado normal botón.</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" s="16" t="inlineStr">
+        <is>
+          <t>Botón redondeado púrpura con brillo superior y sombra base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>button_hover</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Botón Hover</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>32×32 / 9-slice</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/button_hover.png</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Madera más brillante</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Estado hover.</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>Botón púrpura claro con destello (estado hover).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>button_pressed</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Botón Pressed</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>32×32 / 9-slice</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/button_pressed.png</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Madera oscura hundida</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Estado pulsado.</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" s="16" t="inlineStr">
+        <is>
+          <t>Botón púrpura oscuro hundido (estado pressed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>badge_new</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Badge Nuevo</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Badge</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/badge_new.png</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Rojo con texto NEW</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Notifica novedad.</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" s="16" t="inlineStr">
+        <is>
+          <t>Círculo rojo con '!' blanca (novedad).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>badge_vip</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Badge VIP</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Badge</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/badge_vip.png</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Dorado con corona</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Indica cliente VIP.</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" s="16" t="inlineStr">
+        <is>
+          <t>Círculo dorado con estrella blanca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>badge_event</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Badge Evento</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Badge</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/badge_event.png</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Púrpura con estrella</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Indica evento activo.</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="inlineStr">
+        <is>
+          <t>Círculo púrpura con rayo dorado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>progress_bar_fill</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Progress Bar Fill</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>9-slice</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/progress_bar_fill.png</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Verde con brillo</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Relleno de barra.</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" s="16" t="inlineStr">
+        <is>
+          <t>Barra dorada con brillo superior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>progress_bar_bg</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Progress Bar Background</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>9-slice</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>art/sprites/ui/progress_bar_bg.png</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Marrón oscuro hueco</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Fondo de barra.</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" s="16" t="inlineStr">
+        <is>
+          <t>Barra hundida oscura con borde violeta.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1843,7 +3855,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4341,7 +6353,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5431,7 +7443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6185,7 +8197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6451,7 +8463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6758,13 +8770,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6775,6 +8787,7 @@
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -6818,6 +8831,11 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Descripción Sprite</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -6860,6 +8878,11 @@
           <t>Ya en uso</t>
         </is>
       </c>
+      <c r="I2" s="16" t="inlineStr">
+        <is>
+          <t>Espíritu púrpura amistoso con colita ondulada, brillo interior y chispa dorada sobre la cabeza.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -6902,6 +8925,11 @@
           <t>Cosmético</t>
         </is>
       </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>Gato dorado sentado: orejas rosadas, pechito crema, cola curvada y naricita rosa.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -6944,6 +8972,11 @@
           <t>Cosmético</t>
         </is>
       </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>Búho marrón: discos faciales crema, panza moteada dorada, alas plegadas y patitas doradas.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -6986,6 +9019,11 @@
           <t>Cosmético</t>
         </is>
       </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Dragoncito rojo: cuernitos y panza dorados, alitas rosadas, cola con punta de flecha dorada.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -7028,6 +9066,11 @@
           <t>Cosmético</t>
         </is>
       </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>Slime cyan translúcido con brillo interior, burbujitas blancas y carita sonriente.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -7068,6 +9111,11 @@
       <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Cosmético</t>
+        </is>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>Hadita: pelo rosa con moñito, vestidito rosa, alas iridiscentes cyan/lila y chispas doradas alrededor.</t>
         </is>
       </c>
     </row>
@@ -7871,7 +9919,231 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>REGLAS DEL PIXEL ART COZY — MYSTIC EMPORIUM</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="B2" s="16" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Pitch unificado</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>1 píxel de arte = 2 píxeles de pantalla. Assets 64×64 y 40×40 se dibujan a media resolución y se escalan ×2 NEAREST; NPCs 32×48, decoraciones e items se dibujan nativos (sus escenas ya escalan ×2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dimensiones</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Cada PNG conserva SIEMPRE sus dimensiones exactas actuales; las escenas usan AtlasTextures con regiones fijas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Contorno</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Contorno sticker de 1 px color #2b1b35 (violeta cálido, nunca negro puro), dibujado POR DEBAJO de los rellenos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Paleta arcana</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Púrpuras #3a2058 / #6e3aa0 / #9d6dff / #c89bff — color identidad de la tienda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Paleta dorada</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Dorados #855a14 / #d27d2c / #f0c060 (+#f8e0a0 highlight) — monedas, magia, madera cálida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Acentos</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Cyan #6dc2ca, rojo #d04648, azul #597dce, verde #6daa2c + tonos DB16. Piedra #757161/#8595a1, piel #d2aa99, madera #855a14/#a87848.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Caritas chibi</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Ojos 2×2 con brillo blanco arriba-izquierda, blush rosa #f0a0b0 a los lados, sonrisita de 2 px. Cabeza grande (~40% de la altura).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Animación idle</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>4 frames: bob vertical [0,1,1,0] + parpadeo en frame 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Animación walk</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>6 frames: piernas alternas [-1,-1,0,0,0,0]/[0,0,0,-1,-1,0], bob [0,-1,0,0,-1,0], brazos en swing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Anim ambiente</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Parcelas/caldero/forja: 6 frames horizontales, pulso suave + chispa/burbuja periódica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tiles</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Patrones seamless (aritmética modular); verificar repetición 2×2 antes de exportar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Madera con veta, piedra moteada (hash espacial, no lineal), vidrio translúcido con brillo diagonal 2 px, metal con highlight superior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Fuente de luz arriba-izquierda: highlight en esa esquina, sombra propia abajo-derecha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Transparencias</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Espíritus/vidrio/overlays con alpha 120–230; sombras de contacto alpha ~90.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Generador PIL en ~/Proyectos/sd-pixel/cozy_all/ (un módulo por lote). Regenerar → copiar a godot/art/ → godot --headless --import → validar con movie mode.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7886,6 +10158,7 @@
     <col width="34" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -7949,6 +10222,11 @@
           <t>Animación</t>
         </is>
       </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>Descripción Sprite</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
@@ -8001,6 +10279,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M2" s="16" t="inlineStr">
+        <is>
+          <t>Frasco pequeño oliva ámbar con corcho.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -8053,6 +10336,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>Vial alto lila luminoso con burbuja.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
@@ -8105,6 +10393,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>Colgante de cordón con engaste dorado y gema cyan.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
@@ -8157,6 +10450,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M5" s="16" t="inlineStr">
+        <is>
+          <t>Anillo dorado de doble aro con gema azul y destello.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
@@ -8209,6 +10507,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>Vial alto verde brillante con corcho.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
@@ -8265,6 +10568,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>Moneda dorada con anillo interior y símbolo grabado, brillo arriba.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
@@ -8317,6 +10625,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>Arco curvo de madera con cuerda crema y flecha lista.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
@@ -8369,6 +10682,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>Bastón de madera diagonal con orbe púrpura y chispas doradas.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
@@ -8421,6 +10739,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>Bomba esférica negra con mecha encendida y nubecita de humo.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="21" t="inlineStr">
@@ -8473,6 +10796,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>Par de botas marrón con suela clara y alitas blancas.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
@@ -8525,6 +10853,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>Brazalete dorado de tres aros con gema roja.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="inlineStr">
@@ -8577,6 +10910,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>Brújula dorada con esfera crema y aguja roja/azul.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
@@ -8629,6 +10967,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>Capa gris-morada oscura ondulante con broche dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="21" t="inlineStr">
@@ -8681,6 +11024,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>Casco de hierro con visor oscuro, runa cyan y penacho rojo.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
@@ -8733,6 +11081,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>Seta de sombrero rojo con motas blancas y pie crema.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="21" t="inlineStr">
@@ -8785,6 +11138,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>Cúmulo de 3 cristales púrpura facetados sobre base de roca.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
@@ -8841,6 +11199,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>Estrella dorada de 4 puntas con destellos.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="inlineStr">
@@ -8893,6 +11256,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>Cúmulo cyan claro de 2 cristales con destello blanco.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
@@ -8945,6 +11313,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>Cuerno espiral marfil con punta brillante y base dorada.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="inlineStr">
@@ -8997,6 +11370,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>Piel curtida marrón claro extendida con clavos en las esquinas.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
@@ -9049,6 +11427,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>Daga con hoja lila, guarda dorada y chispas púrpura.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
@@ -9101,6 +11484,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>Frasco grande rojo vivo con banda dorada y brillo intenso.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
@@ -9153,6 +11541,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>Escama roja en forma de gota invertida con brillo y estrías.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
@@ -9205,6 +11598,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>Escudo azul con marco dorado y emblema dorado central.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
@@ -9257,6 +11655,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>Orbe flotante cyan translúcido con núcleo claro, chispas doradas y sombra suave.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
@@ -9309,6 +11712,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>Orbe púrpura con núcleo lila y chispas cyan.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
@@ -9361,6 +11769,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>Orbe dorado claro radiante con chispas blancas.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="inlineStr">
@@ -9413,6 +11826,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>Orbe gris-morado oscuro con chispas lila.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
@@ -9465,6 +11883,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>Espada diagonal plateada con filo claro, guarda dorada y chispas cyan.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="21" t="inlineStr">
@@ -9517,6 +11940,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>Gran estrella dorada clara radiante — el item legendario final.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="21" t="inlineStr">
@@ -9569,6 +11997,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>Girasol de 8 pétalos dorados, centro marrón, tallo con hojas.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="21" t="inlineStr">
@@ -9621,6 +12054,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>Rombo púrpura facetado con arista lila.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
@@ -9673,6 +12111,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>Rombo negro violáceo con arista gris.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="21" t="inlineStr">
@@ -9725,6 +12168,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>Figurita de arcilla marrón con ojos y runa de pecho cyan.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
@@ -9777,6 +12225,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>Manojo de 3 tallos con hojas cyan atado con cordel de madera.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="21" t="inlineStr">
@@ -9829,6 +12282,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>Carrete de madera con hilo púrpura y hebra suelta con chispa.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="21" t="inlineStr">
@@ -9881,6 +12339,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>Hueso blanco clásico de doble nudillo en diagonal.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="inlineStr">
@@ -9933,6 +12396,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M39" s="16" t="inlineStr">
+        <is>
+          <t>Tarjeta crema con marco dorado, líneas de texto y sello de lacre rojo.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
@@ -9985,6 +12453,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M40" s="16" t="inlineStr">
+        <is>
+          <t>Lágrima cyan con brillo blanco y destellos alrededor.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
@@ -10037,6 +12510,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>Lanza esbelta con punta de hoja élfica verde-plateada y amarre dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
@@ -10089,6 +12567,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>Grimorio púrpura con lomo oscuro, marco dorado y gema lila central.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
@@ -10141,6 +12624,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>Lingote 3D gris hierro con cara superior iluminada.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="inlineStr">
@@ -10193,6 +12681,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>Lingote cyan metálico, el más exótico.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="inlineStr">
@@ -10245,6 +12738,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>Lingote dorado con brillo blanco superior.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="21" t="inlineStr">
@@ -10297,6 +12795,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>Lingote gris plata con cara superior casi blanca.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="21" t="inlineStr">
@@ -10349,6 +12852,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>Linterna de hierro con luz dorada cálida, asa y destellos.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="21" t="inlineStr">
@@ -10401,6 +12909,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>Llave dorada diagonal con ojo anillado y dientes, destello blanco.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="21" t="inlineStr">
@@ -10453,6 +12966,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M49" s="16" t="inlineStr">
+        <is>
+          <t>Tronco de madera con anillos visibles y motas púrpura brillantes.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
@@ -10505,6 +13023,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>Mapa crema con bordes enrollados dorados, isla verde, ruta punteada roja y X.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="21" t="inlineStr">
@@ -10557,6 +13080,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>Roca gris redondeada con vetas metálicas claras y destellos.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="21" t="inlineStr">
@@ -10609,6 +13137,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>Roca gris con motas cyan brillantes.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="21" t="inlineStr">
@@ -10661,6 +13194,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>Roca gris con motas doradas brillantes.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="21" t="inlineStr">
@@ -10713,6 +13251,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>Manojo púrpura oscuro de hojas puntiagudas con puntas lila.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="21" t="inlineStr">
@@ -10765,6 +13308,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M55" s="16" t="inlineStr">
+        <is>
+          <t>Tarro de vidrio con pasta verde oliva y tapa de madera clara.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="21" t="inlineStr">
@@ -10817,6 +13365,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>Pergamino enrollado crema con cinta gris, sin runa (en blanco).</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="21" t="inlineStr">
@@ -10869,6 +13422,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M57" s="16" t="inlineStr">
+        <is>
+          <t>Pergamino con cinta verde y runa verde claro.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="21" t="inlineStr">
@@ -10921,6 +13479,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M58" s="16" t="inlineStr">
+        <is>
+          <t>Pergamino con cinta roja y runa naranja fuego.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="21" t="inlineStr">
@@ -10973,6 +13536,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M59" s="16" t="inlineStr">
+        <is>
+          <t>Pergamino con cinta cyan y runa cyan claro.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="21" t="inlineStr">
@@ -11025,6 +13593,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M60" s="16" t="inlineStr">
+        <is>
+          <t>Pergamino con cinta dorada y runa dorada.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="21" t="inlineStr">
@@ -11077,6 +13650,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M61" s="16" t="inlineStr">
+        <is>
+          <t>Pergamino con cinta púrpura y runa lila.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="21" t="inlineStr">
@@ -11129,6 +13707,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M62" s="16" t="inlineStr">
+        <is>
+          <t>Tarro con pigmento cyan profundo y pluma.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="21" t="inlineStr">
@@ -11181,6 +13764,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M63" s="16" t="inlineStr">
+        <is>
+          <t>Lingote blanco plateado luminoso.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="21" t="inlineStr">
@@ -11233,6 +13821,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M64" s="16" t="inlineStr">
+        <is>
+          <t>Pluma dorada diagonal con raquis blanco y cálamo dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="21" t="inlineStr">
@@ -11285,6 +13878,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M65" s="16" t="inlineStr">
+        <is>
+          <t>Frasco redondo grande rojo con banda dorada, corcho y brillo.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="21" t="inlineStr">
@@ -11337,6 +13935,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M66" s="16" t="inlineStr">
+        <is>
+          <t>Frasco redondo pequeño rojo coral con corcho, brillo de vidrio y burbuja.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="21" t="inlineStr">
@@ -11389,6 +13992,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M67" s="16" t="inlineStr">
+        <is>
+          <t>Frasco redondo naranja con corcho de madera.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="21" t="inlineStr">
@@ -11441,6 +14049,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M68" s="16" t="inlineStr">
+        <is>
+          <t>Frasco grande rojo ladrillo con banda dorada.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="21" t="inlineStr">
@@ -11493,6 +14106,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M69" s="16" t="inlineStr">
+        <is>
+          <t>Frasco pequeño naranja, versión compacta.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="21" t="inlineStr">
@@ -11545,6 +14163,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M70" s="16" t="inlineStr">
+        <is>
+          <t>Vial alto casi transparente: solo vidrio, corcho y un brillo.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="21" t="inlineStr">
@@ -11597,6 +14220,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M71" s="16" t="inlineStr">
+        <is>
+          <t>Frasco redondo azul con brillo cyan y burbujita.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="21" t="inlineStr">
@@ -11649,6 +14277,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M72" s="16" t="inlineStr">
+        <is>
+          <t>Frasco redondo gris piedra, sobrio y robusto.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="21" t="inlineStr">
@@ -11701,6 +14334,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M73" s="16" t="inlineStr">
+        <is>
+          <t>Vial alto y esbelto cyan con aire arriba y brillo.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="21" t="inlineStr">
@@ -11753,6 +14391,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M74" s="16" t="inlineStr">
+        <is>
+          <t>Saquito de cuero atado con polvo dorado asomando y chispas blancas.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="21" t="inlineStr">
@@ -11805,6 +14448,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M75" s="16" t="inlineStr">
+        <is>
+          <t>Saquito de cuero con polvo crema pálido.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="21" t="inlineStr">
@@ -11857,6 +14505,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M76" s="16" t="inlineStr">
+        <is>
+          <t>Saquito con polvo cyan claro y chispas lila.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="21" t="inlineStr">
@@ -11909,6 +14562,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M77" s="16" t="inlineStr">
+        <is>
+          <t>Raíz antropomorfa beige dormida (ojitos cerrados) con hojas verdes arriba.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="21" t="inlineStr">
@@ -11961,6 +14619,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M78" s="16" t="inlineStr">
+        <is>
+          <t>Reloj de arena de madera con arena cyan y chispas mágicas lila.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="21" t="inlineStr">
@@ -12013,6 +14676,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M79" s="16" t="inlineStr">
+        <is>
+          <t>Gota de resina ámbar dorada con brillo, gotita separada y destello.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="21" t="inlineStr">
@@ -12065,6 +14733,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M80" s="16" t="inlineStr">
+        <is>
+          <t>Montoncito de sal blanca en platito crema con destellos cyan.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="21" t="inlineStr">
@@ -12117,6 +14790,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M81" s="16" t="inlineStr">
+        <is>
+          <t>Vial alto rojo muy oscuro con reflejo granate.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="21" t="inlineStr">
@@ -12169,6 +14847,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M82" s="16" t="inlineStr">
+        <is>
+          <t>Tablón de madera con veta y runas cyan grabadas.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="21" t="inlineStr">
@@ -12221,6 +14904,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M83" s="16" t="inlineStr">
+        <is>
+          <t>Colgante de gema verde con cordón dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="21" t="inlineStr">
@@ -12273,6 +14961,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M84" s="16" t="inlineStr">
+        <is>
+          <t>Tarro de vidrio con tinta púrpura oscura, tapa de hierro y pluma blanca.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="22" t="inlineStr">
@@ -12329,6 +15022,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M85" s="16" t="inlineStr">
+        <is>
+          <t>Moneda púrpura con estrella lila grabada.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="21" t="inlineStr">
@@ -12381,6 +15079,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="M86" s="16" t="inlineStr">
+        <is>
+          <t>Cepo de hierro con dientes plateados, placa dorada y chispas púrpura.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="22" t="inlineStr">
@@ -12435,6 +15138,11 @@
       <c r="L87" s="22" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="M87" s="16" t="inlineStr">
+        <is>
+          <t>Tarjeta con marco azul, texto y sello azul oscuro.</t>
         </is>
       </c>
     </row>
@@ -12443,13 +15151,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -12463,6 +15171,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -12521,6 +15230,11 @@
           <t>Animación</t>
         </is>
       </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>Descripción Sprite</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
@@ -12572,6 +15286,11 @@
           <t>idle + walk_south</t>
         </is>
       </c>
+      <c r="L2" s="16" t="inlineStr">
+        <is>
+          <t>Chibi verde brillante: capucha puntiaguda con hojita que se mece, orejas élficas, túnica verde y manojo de hierbas en la mano. Idle 4 (bob+parpadeo) + walk 6.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -12623,6 +15342,11 @@
           <t>idle</t>
         </is>
       </c>
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t>Roca redonda gris con cúmulo de amatista en la espalda, ojos dormidos cerrados y musgo; estático 64×64.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
@@ -12674,6 +15398,11 @@
           <t>idle</t>
         </is>
       </c>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>Chibi púrpura de mago: sombrero puntiagudo con estrella dorada, túnica púrpura y libro abierto. Grid 288×480 (idle 4 / walk 6).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
@@ -12729,6 +15458,11 @@
           <t>idle + walk_south</t>
         </is>
       </c>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>Chibi leñador: gorro rojo con pompón, chaleco marrón sobre camisa verde y hacha vertical al costado. Idle 4 + walk 6.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
@@ -12784,6 +15518,11 @@
           <t>idle + walk_south</t>
         </is>
       </c>
+      <c r="L6" s="16" t="inlineStr">
+        <is>
+          <t>Wisp cyan en forma de lágrima flotante con gema rombo púrpura en la frente, cola que ondula y sombra en el suelo; sin piernas. Idle 4 + walk 6.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="inlineStr">
@@ -12835,6 +15574,11 @@
           <t>idle + walk</t>
         </is>
       </c>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>Chibi del jugador: pelo castaño, delantal azul con hebilla dorada y capa púrpura a los lados. Grid 288×480 (idle 4 / walk 6).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
@@ -12884,6 +15628,11 @@
       <c r="K8" s="21" t="inlineStr">
         <is>
           <t>static</t>
+        </is>
+      </c>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>Viajero genérico: capa parda con capucha bajada, bolsa al hombro con broche dorado. Grid 288×480; en juego se re-skinea con los NPCs.</t>
         </is>
       </c>
     </row>
@@ -12892,13 +15641,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12913,6 +15662,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -12976,6 +15726,11 @@
           <t>Animación</t>
         </is>
       </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>Descripción Sprite</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -13034,6 +15789,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M2" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica con cinturón marrón, sombrero de paja, pelo corto castaño oscuro.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -13092,6 +15852,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica con cinturón marrón, capa verde, pelo de puntas castaño, espada.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -13150,6 +15915,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: armadura marrón, pelo corto castaño oscuro, cicatriz, espada.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -13208,6 +15978,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M5" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: traje de color especial, pelo corto castaño oscuro, barba castaño oscuro, monedero.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -13266,6 +16041,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica gris, pelo corto blanco, barba larga blanco, bastón con gema luminosa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -13324,6 +16104,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: pequeño (cuerpo de niño/halfling), túnica con cinturón rojo, pelo de puntas castaño.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -13382,6 +16167,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: traje blanco, gorro de chef blanco.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -13440,6 +16230,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica blanco, ribetes rojo, pelo corto castaño oscuro, libro.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -13498,6 +16293,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop · Salute 5f one-shot</t>
         </is>
       </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: armadura de color especial, capa rojo, casco con penacho, espada.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -13556,6 +16356,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: armadura dorado, capa blanco, casco con penacho, espada.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -13614,6 +16419,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop · Cast 5f one-shot · Aura idle 4f loop</t>
         </is>
       </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica azul, sombrero puntiagudo de mago, bastón con gema luminosa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -13672,6 +16482,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop · Cast 5f one-shot · Aura idle 4f loop</t>
         </is>
       </c>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica púrpura, ribetes dorado, runas dorado bordadas, sombrero puntiagudo de mago, barba blanco, bastón con gema luminosa.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -13730,6 +16545,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica verde, runas verde claro bordadas, astas de ciervo, melena larga castaño, bastón con gema luminosa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -13788,6 +16608,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: traje de color especial, sombrero con pluma, pelo corto dorado, laúd.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -13846,6 +16671,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica blanco, ribetes dorado, pelo corto gris claro, libro.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -13908,6 +16738,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica con cinturón negro, capucha, daga.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -13966,6 +16801,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: traje de color especial, tricornio negro con pluma, barba castaño oscuro, parche en el ojo.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -14024,6 +16864,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica con cinturón negro, bandana, máscara, daga.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -14086,6 +16931,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop · Salute 5f one-shot</t>
         </is>
       </c>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: armadura negro, capa púrpura oscuro, casco con penacho, espada.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -14144,6 +16994,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica con cinturón verde, melena larga dorado, orejas élficas.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -14202,6 +17057,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica con cinturón negro, melena larga blanco, orejas élficas, piel de color distintivo.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -14260,6 +17120,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: bajo y fornido, túnica con cinturón marrón, pelo corto, barba larga , martillo de forja.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -14318,6 +17183,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: armadura marrón, pelo de puntas negro, colmillos de orco, piel de color distintivo.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -14376,6 +17246,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: pequeño (cuerpo de niño/halfling), túnica con cinturón de color especial, pelo corto castaño.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -14434,6 +17309,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: pequeño (cuerpo de niño/halfling), vestido rosa, flor en el pelo, moño dorado, alas iridiscentes cyan/rosa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -14492,6 +17372,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica negro, runas verde claro bordadas, capucha.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -14554,6 +17439,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: traje negro, capa rojo oscuro, pelo corto negro, colmillos, piel de color distintivo.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -14616,6 +17506,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica con cinturón marrón, orejas animales, cola.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -14674,6 +17569,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: espectral y translúcido, túnica de color especial.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -14736,6 +17636,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica con cinturón rojo, cuernos, cola, piel de color distintivo, tridente dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -14798,6 +17703,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica blanco, ribetes dorado, halo dorado, melena larga dorado, alas de plumas blancas.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -14856,6 +17766,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: esqueleto de cráneo blanco, túnica con cinturón marrón, capa .</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -14918,6 +17833,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: cuerpo de humo sin piernas, túnica de color especial, turbante con joya.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -14980,6 +17900,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: vestido rosa, tiara dorada, melena larga dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -15042,6 +17967,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: traje azul, capa azul oscuro, pelo corto dorado, espada.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -15104,6 +18034,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop · Manto ondea 5f loop</t>
         </is>
       </c>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica púrpura, ribetes blanco, capa rojo oscuro, corona dorada con gemas, barba gris claro.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -15166,6 +18101,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop · Manto ondea 5f loop</t>
         </is>
       </c>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: vestido púrpura, ribetes dorado, corona dorada con gemas, moño castaño oscuro.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -15228,6 +18168,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M39" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica dorado, ribetes rojo, capa rojo oscuro, corona dorada con gemas, barba castaño oscuro.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -15290,6 +18235,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M40" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: traje azul, fedora, lupa dorada.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -15352,6 +18302,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica con cinturón negro, capucha, máscara, daga.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -15414,6 +18369,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: traje gris, moño castaño oscuro, portafolios.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -15472,6 +18432,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: traje marrón, fedora, libreta.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -15530,6 +18495,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: traje negro, pelo corto gris claro, barba gris claro, monóculo dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -15592,6 +18562,11 @@
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
         </is>
       </c>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: túnica de color especial, capucha, rostro en sombra con ojos brillantes.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -15648,6 +18623,11 @@
       <c r="L46" s="17" t="inlineStr">
         <is>
           <t>Idle 4f loop · Walk 6f loop (4-dir) · Sit estático · Happy 4f one-shot · Impatient 4f loop</t>
+        </is>
+      </c>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>Chibi 32×48: vestido de color especial, ribetes dorado, tiara dorada, melena larga.</t>
         </is>
       </c>
     </row>
@@ -15656,13 +18636,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L148"/>
+  <dimension ref="A1:M148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -15677,6 +18657,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -15740,6 +18721,11 @@
           <t>Animación</t>
         </is>
       </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>Descripción Sprite</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
@@ -15794,6 +18780,11 @@
         </is>
       </c>
       <c r="L2" s="21" t="inlineStr"/>
+      <c r="M2" s="16" t="inlineStr">
+        <is>
+          <t>Dos árboles frondosos verdes sobre parche de pasto; versión parcela animada con árbol que pulsa (6 frames).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
@@ -15848,6 +18839,11 @@
         </is>
       </c>
       <c r="L3" s="19" t="inlineStr"/>
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>Altar de piedra clara con luna creciente cyan flotante y chispas; parcela animada 6 frames.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
@@ -15902,6 +18898,11 @@
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr"/>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>Cúmulo de cristales púrpura de 3 puntas sobre tierra; pulsa y destella (6 frames).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
@@ -15956,6 +18957,11 @@
         </is>
       </c>
       <c r="L5" s="19" t="inlineStr"/>
+      <c r="M5" s="16" t="inlineStr">
+        <is>
+          <t>Cuenco de piedra oscura con lava naranja y llama bailando (6 frames).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
@@ -16010,6 +19016,11 @@
         </is>
       </c>
       <c r="L6" s="19" t="inlineStr"/>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>Geoda gris abierta con interior púrpura y cristales; destello periódico.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="inlineStr">
@@ -16064,6 +19075,11 @@
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr"/>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>Parcela de tierra con 3 matas verdes que crecen y se mecen (6 frames).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
@@ -16118,6 +19134,11 @@
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr"/>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>Roca gris con vetas metálicas brillantes sobre parcela.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
@@ -16172,6 +19193,11 @@
         </is>
       </c>
       <c r="L9" s="19" t="inlineStr"/>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>Pozo circular de piedra con remolino púrpura y destello giratorio.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
@@ -16226,6 +19252,11 @@
         </is>
       </c>
       <c r="L10" s="19" t="inlineStr"/>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>Torii rojo en miniatura con espíritu cyan flotando entre los postes.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="21" t="inlineStr">
@@ -16280,6 +19311,11 @@
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr"/>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>Manzano frondoso con manzanas rojas y tronco claro.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
@@ -16334,6 +19370,11 @@
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr"/>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>Pila de piedra para pájaros con agua celeste y pajarito dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="inlineStr">
@@ -16388,6 +19429,11 @@
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr"/>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>Comedero con techito rojo, semillas doradas y poste.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
@@ -16442,6 +19488,11 @@
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr"/>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>Casita de pájaros con techo rojo, agujero oscuro y palito.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="21" t="inlineStr">
@@ -16496,6 +19547,11 @@
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr"/>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>Bonsái de tronco curvo con dos copas verdes en maceta terracota.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
@@ -16550,6 +19606,11 @@
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr"/>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>Brasero de hierro con llama naranja y pie alto.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="21" t="inlineStr">
@@ -16604,6 +19665,11 @@
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr"/>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>Frasco de vidrio con dos mariposas (rosa y cyan).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="21" t="inlineStr">
@@ -16658,6 +19724,11 @@
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr"/>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>Compostera de tablones con compost oscuro y brote verde.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="inlineStr">
@@ -16712,6 +19783,11 @@
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr"/>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>Cúmulo de 3 cristales púrpura sobre roca.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
@@ -16766,6 +19842,11 @@
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr"/>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>Maceta terracota con flor rosa de centro dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="inlineStr">
@@ -16820,6 +19901,11 @@
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr"/>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>Jarrón cyan con 3 flores (rosa, dorada, roja).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
@@ -16874,6 +19960,11 @@
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr"/>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>Fuente de piedra con pila de agua celeste y chorro central.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
@@ -16928,6 +20019,11 @@
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr"/>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>Arco de jardín con enredadera verde y flores rosas/rojas.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
@@ -16982,6 +20078,11 @@
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr"/>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>Banco de jardín de madera con patas de hierro.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
@@ -17036,6 +20137,11 @@
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr"/>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>Gnomo de jardín: gorro rojo, barba blanca, chaqueta azul y mejillas rosadas.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
@@ -17090,6 +20196,11 @@
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr"/>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>Parcela de cultivo con surcos y brotecitos verdes.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
@@ -17144,6 +20255,11 @@
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr"/>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>Estanque ovalado celeste con nenúfar y flor rosa.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
@@ -17198,6 +20314,11 @@
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr"/>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>Seta roja con motas blancas y pie crema.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="inlineStr">
@@ -17252,6 +20373,11 @@
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr"/>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>Palmera de interior con 5 frondas verdes en maceta terracota.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
@@ -17306,6 +20432,11 @@
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr"/>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>Pétalos rosa dispersos por el suelo con uno dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="21" t="inlineStr">
@@ -17360,6 +20491,11 @@
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr"/>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>Planta grande de tres copas verdes en maceta terracota.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="21" t="inlineStr">
@@ -17414,6 +20550,11 @@
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr"/>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>Calabaza naranja con gajos, tallo verde y brillo.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="21" t="inlineStr">
@@ -17468,6 +20609,11 @@
         </is>
       </c>
       <c r="L33" s="21" t="inlineStr"/>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>Poza de agua celeste con borde de piedra, brillo y onda.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
@@ -17522,6 +20668,11 @@
         </is>
       </c>
       <c r="L34" s="21" t="inlineStr"/>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>Mesa de madera sencilla con travesaño.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="21" t="inlineStr">
@@ -17576,6 +20727,11 @@
         </is>
       </c>
       <c r="L35" s="21" t="inlineStr"/>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>Estantería de madera 32×32 con 3 filas de libros de colores.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
@@ -17630,6 +20786,11 @@
         </is>
       </c>
       <c r="L36" s="21" t="inlineStr"/>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>Caldero de hierro con brebaje verde burbujeante y llamas debajo (6 frames).</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="21" t="inlineStr">
@@ -17684,6 +20845,11 @@
         </is>
       </c>
       <c r="L37" s="21" t="inlineStr"/>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>Cofre de madera con banda dorada, cerradura y tapa abombada.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="21" t="inlineStr">
@@ -17734,6 +20900,11 @@
       </c>
       <c r="K38" s="21" t="inlineStr"/>
       <c r="L38" s="21" t="inlineStr"/>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>Escritorio de madera con pergamino, tintero y pluma.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="inlineStr">
@@ -17788,6 +20959,11 @@
         </is>
       </c>
       <c r="L39" s="21" t="inlineStr"/>
+      <c r="M39" s="16" t="inlineStr">
+        <is>
+          <t>Forja de piedra con boca incandescente que pulsa, chimenea y chispas (6 frames).</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
@@ -17838,6 +21014,11 @@
       </c>
       <c r="K40" s="21" t="inlineStr"/>
       <c r="L40" s="21" t="inlineStr"/>
+      <c r="M40" s="16" t="inlineStr">
+        <is>
+          <t>Libro de hechizos púrpura 16×16 con runas doradas.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
@@ -17892,6 +21073,11 @@
         </is>
       </c>
       <c r="L41" s="21" t="inlineStr"/>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>Altar de piedra con paño crema, cáliz dorado y destellos cyan.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
@@ -17946,6 +21132,11 @@
         </is>
       </c>
       <c r="L42" s="21" t="inlineStr"/>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>Astas de ciervo marfil montadas en placa de madera.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
@@ -18000,6 +21191,11 @@
         </is>
       </c>
       <c r="L43" s="21" t="inlineStr"/>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>Ventana arqueada de piedra con vidrio celeste y parteluz.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="inlineStr">
@@ -18054,6 +21250,11 @@
         </is>
       </c>
       <c r="L44" s="21" t="inlineStr"/>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>Cama con dosel púrpura, cortina, manta roja y almohada crema.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="inlineStr">
@@ -18108,6 +21309,11 @@
         </is>
       </c>
       <c r="L45" s="21" t="inlineStr"/>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>Cama individual con cabecera de madera, manta azul y almohada.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="21" t="inlineStr">
@@ -18162,6 +21368,11 @@
         </is>
       </c>
       <c r="L46" s="21" t="inlineStr"/>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>Baúl de madera con manta roja doblada asomando.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="21" t="inlineStr">
@@ -18216,6 +21427,11 @@
         </is>
       </c>
       <c r="L47" s="21" t="inlineStr"/>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>Vela blanca con llama bailando, cera derretida y platito dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="21" t="inlineStr">
@@ -18270,6 +21486,11 @@
         </is>
       </c>
       <c r="L48" s="21" t="inlineStr"/>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>Círculo de tiza blanca con anillo interior y marcas rituales.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="21" t="inlineStr">
@@ -18324,6 +21545,11 @@
         </is>
       </c>
       <c r="L49" s="21" t="inlineStr"/>
+      <c r="M49" s="16" t="inlineStr">
+        <is>
+          <t>Pizarra verde con marco de madera, escritura y tiza.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
@@ -18378,6 +21604,11 @@
         </is>
       </c>
       <c r="L50" s="21" t="inlineStr"/>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>Baldosa ajedrez crema/gris de 8px.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="21" t="inlineStr">
@@ -18432,6 +21663,11 @@
         </is>
       </c>
       <c r="L51" s="21" t="inlineStr"/>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>Tablero de ajedrez en miniatura con piezas blanca y negra.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="21" t="inlineStr">
@@ -18486,6 +21722,11 @@
         </is>
       </c>
       <c r="L52" s="21" t="inlineStr"/>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>Reloj de pared redondo de madera con esfera crema y 12 marcas.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="21" t="inlineStr">
@@ -18540,6 +21781,11 @@
         </is>
       </c>
       <c r="L53" s="21" t="inlineStr"/>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>Relojito redondo dorado con esfera crema.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="21" t="inlineStr">
@@ -18594,6 +21840,11 @@
         </is>
       </c>
       <c r="L54" s="21" t="inlineStr"/>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>Perchero de madera con capa púrpura colgada y broche dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="21" t="inlineStr">
@@ -18648,6 +21899,11 @@
         </is>
       </c>
       <c r="L55" s="21" t="inlineStr"/>
+      <c r="M55" s="16" t="inlineStr">
+        <is>
+          <t>Rosa de los vientos con aro dorado, N roja y S crema.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="21" t="inlineStr">
@@ -18702,6 +21958,11 @@
         </is>
       </c>
       <c r="L56" s="21" t="inlineStr"/>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>Dos espadas plateadas cruzadas con escudete dorado central.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="21" t="inlineStr">
@@ -18756,6 +22017,11 @@
         </is>
       </c>
       <c r="L57" s="21" t="inlineStr"/>
+      <c r="M57" s="16" t="inlineStr">
+        <is>
+          <t>Bola de cristal lila con visión cyan, soporte dorado y base de madera.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="21" t="inlineStr">
@@ -18810,6 +22076,11 @@
         </is>
       </c>
       <c r="L58" s="21" t="inlineStr"/>
+      <c r="M58" s="16" t="inlineStr">
+        <is>
+          <t>Reloj cucú de madera con techito triangular, puertita y pesas doradas.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="21" t="inlineStr">
@@ -18864,6 +22135,11 @@
         </is>
       </c>
       <c r="L59" s="21" t="inlineStr"/>
+      <c r="M59" s="16" t="inlineStr">
+        <is>
+          <t>Mesa ovalada de madera clara con platito y comida.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="21" t="inlineStr">
@@ -18918,6 +22194,11 @@
         </is>
       </c>
       <c r="L60" s="21" t="inlineStr"/>
+      <c r="M60" s="16" t="inlineStr">
+        <is>
+          <t>Vitrina de vidrio con tesoros: moneda, cristal cyan, poción y gema.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="21" t="inlineStr">
@@ -18972,6 +22253,11 @@
         </is>
       </c>
       <c r="L61" s="21" t="inlineStr"/>
+      <c r="M61" s="16" t="inlineStr">
+        <is>
+          <t>Atrapasueños con aro de madera, red crema, cuenta cyan y 3 plumas.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="21" t="inlineStr">
@@ -19026,6 +22312,11 @@
         </is>
       </c>
       <c r="L62" s="21" t="inlineStr"/>
+      <c r="M62" s="16" t="inlineStr">
+        <is>
+          <t>Cómoda de madera con dos cajones dorados y plantita encima.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="21" t="inlineStr">
@@ -19080,6 +22371,11 @@
         </is>
       </c>
       <c r="L63" s="21" t="inlineStr"/>
+      <c r="M63" s="16" t="inlineStr">
+        <is>
+          <t>Tronco caído con anillos visibles y musgo verde.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="21" t="inlineStr">
@@ -19134,6 +22430,11 @@
         </is>
       </c>
       <c r="L64" s="21" t="inlineStr"/>
+      <c r="M64" s="16" t="inlineStr">
+        <is>
+          <t>Chimenea de piedra con dos llamas, leños y repisa con velita y plantita.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="21" t="inlineStr">
@@ -19188,6 +22489,11 @@
         </is>
       </c>
       <c r="L65" s="21" t="inlineStr"/>
+      <c r="M65" s="16" t="inlineStr">
+        <is>
+          <t>Lámpara de pie con pantalla dorada luminosa y poste de madera.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="21" t="inlineStr">
@@ -19242,6 +22548,11 @@
         </is>
       </c>
       <c r="L66" s="21" t="inlineStr"/>
+      <c r="M66" s="16" t="inlineStr">
+        <is>
+          <t>Baldosa decorativa gris con círculo central cyan.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="21" t="inlineStr">
@@ -19296,6 +22607,11 @@
         </is>
       </c>
       <c r="L67" s="21" t="inlineStr"/>
+      <c r="M67" s="16" t="inlineStr">
+        <is>
+          <t>Foto enmarcada en dorado: paisaje con sol y colina.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="21" t="inlineStr">
@@ -19350,6 +22666,11 @@
         </is>
       </c>
       <c r="L68" s="21" t="inlineStr"/>
+      <c r="M68" s="16" t="inlineStr">
+        <is>
+          <t>Frutero de madera con manzana, naranja y pera.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="21" t="inlineStr">
@@ -19404,6 +22725,11 @@
         </is>
       </c>
       <c r="L69" s="21" t="inlineStr"/>
+      <c r="M69" s="16" t="inlineStr">
+        <is>
+          <t>Globo terráqueo azul con continentes verdes, meridiano dorado y base de madera.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="21" t="inlineStr">
@@ -19458,6 +22784,11 @@
         </is>
       </c>
       <c r="L70" s="21" t="inlineStr"/>
+      <c r="M70" s="16" t="inlineStr">
+        <is>
+          <t>Hamaca crema colgada entre dos postes de madera.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="21" t="inlineStr">
@@ -19512,6 +22843,11 @@
         </is>
       </c>
       <c r="L71" s="21" t="inlineStr"/>
+      <c r="M71" s="16" t="inlineStr">
+        <is>
+          <t>Fardo de heno dorado con dos amarres de cuerda.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="21" t="inlineStr">
@@ -19566,6 +22902,11 @@
         </is>
       </c>
       <c r="L72" s="21" t="inlineStr"/>
+      <c r="M72" s="16" t="inlineStr">
+        <is>
+          <t>Cabecera de cama de madera con tallados dorados.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="21" t="inlineStr">
@@ -19620,6 +22961,11 @@
         </is>
       </c>
       <c r="L73" s="21" t="inlineStr"/>
+      <c r="M73" s="16" t="inlineStr">
+        <is>
+          <t>Reloj de arena de madera con arena dorada cayendo.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="21" t="inlineStr">
@@ -19674,6 +23020,11 @@
         </is>
       </c>
       <c r="L74" s="21" t="inlineStr"/>
+      <c r="M74" s="16" t="inlineStr">
+        <is>
+          <t>Tintero de vidrio con tinta azul oscura y pluma blanca.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="21" t="inlineStr">
@@ -19728,6 +23079,11 @@
         </is>
       </c>
       <c r="L75" s="21" t="inlineStr"/>
+      <c r="M75" s="16" t="inlineStr">
+        <is>
+          <t>Joyero rosa oscuro con cierre dorado y collar asomando.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="21" t="inlineStr">
@@ -19782,6 +23138,11 @@
         </is>
       </c>
       <c r="L76" s="21" t="inlineStr"/>
+      <c r="M76" s="16" t="inlineStr">
+        <is>
+          <t>Cocina de hierro con dos hornillas, horno con llama y tubo.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="21" t="inlineStr">
@@ -19836,6 +23197,11 @@
         </is>
       </c>
       <c r="L77" s="21" t="inlineStr"/>
+      <c r="M77" s="16" t="inlineStr">
+        <is>
+          <t>Farol de hierro con luz dorada, asa y tapa triangular.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="21" t="inlineStr">
@@ -19890,6 +23256,11 @@
         </is>
       </c>
       <c r="L78" s="21" t="inlineStr"/>
+      <c r="M78" s="16" t="inlineStr">
+        <is>
+          <t>Mata de lavanda con espigas lila sobre verde.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="21" t="inlineStr">
@@ -19944,6 +23315,11 @@
         </is>
       </c>
       <c r="L79" s="21" t="inlineStr"/>
+      <c r="M79" s="16" t="inlineStr">
+        <is>
+          <t>Sobre crema con solapa dorada y sello de lacre rojo.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="21" t="inlineStr">
@@ -19998,6 +23374,11 @@
         </is>
       </c>
       <c r="L80" s="21" t="inlineStr"/>
+      <c r="M80" s="16" t="inlineStr">
+        <is>
+          <t>Tocón de madera con anillos concéntricos y brote verde.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="21" t="inlineStr">
@@ -20052,6 +23433,11 @@
         </is>
       </c>
       <c r="L81" s="21" t="inlineStr"/>
+      <c r="M81" s="16" t="inlineStr">
+        <is>
+          <t>Mapa extendido con isla, ruta roja punteada y X del tesoro.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="21" t="inlineStr">
@@ -20106,6 +23492,11 @@
         </is>
       </c>
       <c r="L82" s="21" t="inlineStr"/>
+      <c r="M82" s="16" t="inlineStr">
+        <is>
+          <t>Pedestal de mármol blanco con destello dorado arriba.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="21" t="inlineStr">
@@ -20160,6 +23551,11 @@
         </is>
       </c>
       <c r="L83" s="21" t="inlineStr"/>
+      <c r="M83" s="16" t="inlineStr">
+        <is>
+          <t>Baldosa de mármol claro con vetas grises.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="21" t="inlineStr">
@@ -20214,6 +23610,11 @@
         </is>
       </c>
       <c r="L84" s="21" t="inlineStr"/>
+      <c r="M84" s="16" t="inlineStr">
+        <is>
+          <t>Cráter oscuro con meteorito púrpura brillante al centro y grietas.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="21" t="inlineStr">
@@ -20268,6 +23669,11 @@
         </is>
       </c>
       <c r="L85" s="21" t="inlineStr"/>
+      <c r="M85" s="16" t="inlineStr">
+        <is>
+          <t>Espejo ovalado con marco dorado, reflejo y pie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="21" t="inlineStr">
@@ -20322,6 +23728,11 @@
         </is>
       </c>
       <c r="L86" s="21" t="inlineStr"/>
+      <c r="M86" s="16" t="inlineStr">
+        <is>
+          <t>Mortero de piedra con hierbas molidas verdes y mazo de madera.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="21" t="inlineStr">
@@ -20376,6 +23787,11 @@
         </is>
       </c>
       <c r="L87" s="21" t="inlineStr"/>
+      <c r="M87" s="16" t="inlineStr">
+        <is>
+          <t>Baldosa de mosaico multicolor (cyan/púrpura/dorado/azul).</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="21" t="inlineStr">
@@ -20430,6 +23846,11 @@
         </is>
       </c>
       <c r="L88" s="21" t="inlineStr"/>
+      <c r="M88" s="16" t="inlineStr">
+        <is>
+          <t>Mesita de noche de madera con velita encendida.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="21" t="inlineStr">
@@ -20484,6 +23905,11 @@
         </is>
       </c>
       <c r="L89" s="21" t="inlineStr"/>
+      <c r="M89" s="16" t="inlineStr">
+        <is>
+          <t>Cuadro con marco dorado: cielo azul, luna dorada y colinas verdes.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="21" t="inlineStr">
@@ -20538,6 +23964,11 @@
         </is>
       </c>
       <c r="L90" s="21" t="inlineStr"/>
+      <c r="M90" s="16" t="inlineStr">
+        <is>
+          <t>Guirnalda de banderines triangulares de colores en cuerda.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="21" t="inlineStr">
@@ -20592,6 +24023,11 @@
         </is>
       </c>
       <c r="L91" s="21" t="inlineStr"/>
+      <c r="M91" s="16" t="inlineStr">
+        <is>
+          <t>Mantel de cuadros rojo/blanco con canasta, manzana y baguette.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="21" t="inlineStr">
@@ -20646,6 +24082,11 @@
         </is>
       </c>
       <c r="L92" s="21" t="inlineStr"/>
+      <c r="M92" s="16" t="inlineStr">
+        <is>
+          <t>Pila de cojines: púrpura, rojo, dorado y cyan apilados.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="21" t="inlineStr">
@@ -20700,6 +24141,11 @@
         </is>
       </c>
       <c r="L93" s="21" t="inlineStr"/>
+      <c r="M93" s="16" t="inlineStr">
+        <is>
+          <t>Reloj de bolsillo dorado con cadenita y esfera crema.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="21" t="inlineStr">
@@ -20754,6 +24200,11 @@
         </is>
       </c>
       <c r="L94" s="21" t="inlineStr"/>
+      <c r="M94" s="16" t="inlineStr">
+        <is>
+          <t>Tarro de vidrio con poción púrpura y tapa de madera.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="21" t="inlineStr">
@@ -20808,6 +24259,11 @@
         </is>
       </c>
       <c r="L95" s="21" t="inlineStr"/>
+      <c r="M95" s="16" t="inlineStr">
+        <is>
+          <t>Estante de madera con 8 frascos de pociones de colores en 2 filas.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="21" t="inlineStr">
@@ -20862,6 +24318,11 @@
         </is>
       </c>
       <c r="L96" s="21" t="inlineStr"/>
+      <c r="M96" s="16" t="inlineStr">
+        <is>
+          <t>Tablón de misiones de madera con 3 carteles y chinchetas de colores.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="21" t="inlineStr">
@@ -20916,6 +24377,11 @@
         </is>
       </c>
       <c r="L97" s="21" t="inlineStr"/>
+      <c r="M97" s="16" t="inlineStr">
+        <is>
+          <t>Dos postes dorados con cuerda roja colgante (fila de espera).</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
@@ -20970,6 +24436,11 @@
         </is>
       </c>
       <c r="L98" s="21" t="inlineStr"/>
+      <c r="M98" s="16" t="inlineStr">
+        <is>
+          <t>Pluma blanca en tintero sobre base de madera.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="21" t="inlineStr">
@@ -21024,6 +24495,11 @@
         </is>
       </c>
       <c r="L99" s="21" t="inlineStr"/>
+      <c r="M99" s="16" t="inlineStr">
+        <is>
+          <t>Mesa redonda de madera con centro de mesa y florecita.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="21" t="inlineStr">
@@ -21078,6 +24554,11 @@
         </is>
       </c>
       <c r="L100" s="21" t="inlineStr"/>
+      <c r="M100" s="16" t="inlineStr">
+        <is>
+          <t>Círculo rúnico púrpura de dos anillos con puntos dorados y runa central.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="21" t="inlineStr">
@@ -21132,6 +24613,11 @@
         </is>
       </c>
       <c r="L101" s="21" t="inlineStr"/>
+      <c r="M101" s="16" t="inlineStr">
+        <is>
+          <t>Espantapájaros: cabeza de saco, sombrero de paja, camisa roja y cuervo amistoso.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="21" t="inlineStr">
@@ -21186,6 +24672,11 @@
         </is>
       </c>
       <c r="L102" s="21" t="inlineStr"/>
+      <c r="M102" s="16" t="inlineStr">
+        <is>
+          <t>Estante largo de madera con libros de colores, frasco y cajita.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="21" t="inlineStr">
@@ -21240,6 +24731,11 @@
         </is>
       </c>
       <c r="L103" s="21" t="inlineStr"/>
+      <c r="M103" s="16" t="inlineStr">
+        <is>
+          <t>Calavera blanca amistosa con brillitos cyan en las cuencas.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="21" t="inlineStr">
@@ -21294,6 +24790,11 @@
         </is>
       </c>
       <c r="L104" s="21" t="inlineStr"/>
+      <c r="M104" s="16" t="inlineStr">
+        <is>
+          <t>Trofeo de cráneo de dragón con cuernos y ojos rojos en placa de madera.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="21" t="inlineStr">
@@ -21348,6 +24849,11 @@
         </is>
       </c>
       <c r="L105" s="21" t="inlineStr"/>
+      <c r="M105" s="16" t="inlineStr">
+        <is>
+          <t>Cuenco oscuro con almita cyan flotando y chispas.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="21" t="inlineStr">
@@ -21402,6 +24908,11 @@
         </is>
       </c>
       <c r="L106" s="21" t="inlineStr"/>
+      <c r="M106" s="16" t="inlineStr">
+        <is>
+          <t>Libro de hechizos abierto con tapas púrpura, runas y magia saliendo.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="21" t="inlineStr">
@@ -21456,6 +24967,11 @@
         </is>
       </c>
       <c r="L107" s="21" t="inlineStr"/>
+      <c r="M107" s="16" t="inlineStr">
+        <is>
+          <t>Baldosa nocturna oscura con estrella dorada y destellos.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="21" t="inlineStr">
@@ -21510,6 +25026,11 @@
         </is>
       </c>
       <c r="L108" s="21" t="inlineStr"/>
+      <c r="M108" s="16" t="inlineStr">
+        <is>
+          <t>Montículo de 4 piedras apiladas de mayor a menor.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="21" t="inlineStr">
@@ -21564,6 +25085,11 @@
         </is>
       </c>
       <c r="L109" s="21" t="inlineStr"/>
+      <c r="M109" s="16" t="inlineStr">
+        <is>
+          <t>Camino de 6 piedras planas con pasto asomando.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="21" t="inlineStr">
@@ -21618,6 +25144,11 @@
         </is>
       </c>
       <c r="L110" s="21" t="inlineStr"/>
+      <c r="M110" s="16" t="inlineStr">
+        <is>
+          <t>Cama de paja dorada con hundimiento central y pajitas sueltas.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="21" t="inlineStr">
@@ -21672,6 +25203,11 @@
         </is>
       </c>
       <c r="L111" s="21" t="inlineStr"/>
+      <c r="M111" s="16" t="inlineStr">
+        <is>
+          <t>Glifo de invocación verde: doble anillo, triángulos y runas.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="21" t="inlineStr">
@@ -21726,6 +25262,11 @@
         </is>
       </c>
       <c r="L112" s="21" t="inlineStr"/>
+      <c r="M112" s="16" t="inlineStr">
+        <is>
+          <t>Tapiz púrpura colgante con estrella dorada, luna cyan y borlas.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="21" t="inlineStr">
@@ -21780,6 +25321,11 @@
         </is>
       </c>
       <c r="L113" s="21" t="inlineStr"/>
+      <c r="M113" s="16" t="inlineStr">
+        <is>
+          <t>Mazo de cartas de tarot púrpura con carta volteada (estrella).</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="21" t="inlineStr">
@@ -21834,6 +25380,11 @@
         </is>
       </c>
       <c r="L114" s="21" t="inlineStr"/>
+      <c r="M114" s="16" t="inlineStr">
+        <is>
+          <t>Tetera cyan con tapa dorada, asa y vapor saliendo del pico.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="21" t="inlineStr">
@@ -21888,6 +25439,11 @@
         </is>
       </c>
       <c r="L115" s="21" t="inlineStr"/>
+      <c r="M115" s="16" t="inlineStr">
+        <is>
+          <t>Telescopio dorado en trípode de madera apuntando a una estrella.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="21" t="inlineStr">
@@ -21942,6 +25498,11 @@
         </is>
       </c>
       <c r="L116" s="21" t="inlineStr"/>
+      <c r="M116" s="16" t="inlineStr">
+        <is>
+          <t>Pila de 3 tomos (rojo, azul, verde) con páginas visibles.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="21" t="inlineStr">
@@ -21996,6 +25557,11 @@
         </is>
       </c>
       <c r="L117" s="21" t="inlineStr"/>
+      <c r="M117" s="16" t="inlineStr">
+        <is>
+          <t>Antorcha de pared con llama, cazoleta de hierro y soporte.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="21" t="inlineStr">
@@ -22050,6 +25616,11 @@
         </is>
       </c>
       <c r="L118" s="21" t="inlineStr"/>
+      <c r="M118" s="16" t="inlineStr">
+        <is>
+          <t>Antorcha de estaca clavada en el suelo con llama.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="21" t="inlineStr">
@@ -22104,6 +25675,11 @@
         </is>
       </c>
       <c r="L119" s="21" t="inlineStr"/>
+      <c r="M119" s="16" t="inlineStr">
+        <is>
+          <t>Cofre del tesoro con banda dorada y monedas/gemas asomando.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="21" t="inlineStr">
@@ -22158,6 +25734,11 @@
         </is>
       </c>
       <c r="L120" s="21" t="inlineStr"/>
+      <c r="M120" s="16" t="inlineStr">
+        <is>
+          <t>Tocador con espejo ovalado dorado, perfume y joyita.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="21" t="inlineStr">
@@ -22212,6 +25793,11 @@
         </is>
       </c>
       <c r="L121" s="21" t="inlineStr"/>
+      <c r="M121" s="16" t="inlineStr">
+        <is>
+          <t>Reloj de pared de madera con péndulo dorado visible.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="21" t="inlineStr">
@@ -22266,6 +25852,11 @@
         </is>
       </c>
       <c r="L122" s="21" t="inlineStr"/>
+      <c r="M122" s="16" t="inlineStr">
+        <is>
+          <t>Lámpara de pared con pantalla dorada luminosa y brazo de hierro.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="21" t="inlineStr">
@@ -22320,6 +25911,11 @@
         </is>
       </c>
       <c r="L123" s="21" t="inlineStr"/>
+      <c r="M123" s="16" t="inlineStr">
+        <is>
+          <t>Repisa de pared con libros de colores y escuadras.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="21" t="inlineStr">
@@ -22374,6 +25970,11 @@
         </is>
       </c>
       <c r="L124" s="21" t="inlineStr"/>
+      <c r="M124" s="16" t="inlineStr">
+        <is>
+          <t>Armario de madera de dos puertas con pomos dorados y copete.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="21" t="inlineStr">
@@ -22428,6 +26029,11 @@
         </is>
       </c>
       <c r="L125" s="21" t="inlineStr"/>
+      <c r="M125" s="16" t="inlineStr">
+        <is>
+          <t>Carretilla de madera con rueda de hierro y carga (planta, oro).</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="21" t="inlineStr">
@@ -22482,6 +26088,11 @@
         </is>
       </c>
       <c r="L126" s="21" t="inlineStr"/>
+      <c r="M126" s="16" t="inlineStr">
+        <is>
+          <t>Ventana de madera con cruz central, vidrio celeste y repisa con plantita.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="21" t="inlineStr">
@@ -22536,6 +26147,11 @@
         </is>
       </c>
       <c r="L127" s="21" t="inlineStr"/>
+      <c r="M127" s="16" t="inlineStr">
+        <is>
+          <t>Ventana con cortinas púrpura recogidas con amarres dorados.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="21" t="inlineStr">
@@ -22590,6 +26206,11 @@
         </is>
       </c>
       <c r="L128" s="21" t="inlineStr"/>
+      <c r="M128" s="16" t="inlineStr">
+        <is>
+          <t>Pozo de los deseos: techito rojo, piedra, cubo y moneda cayendo.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="21" t="inlineStr">
@@ -22644,6 +26265,11 @@
         </is>
       </c>
       <c r="L129" s="21" t="inlineStr"/>
+      <c r="M129" s="16" t="inlineStr">
+        <is>
+          <t>Sombrero de bruja púrpura con punta doblada y banda dorada con hebilla.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="21" t="inlineStr">
@@ -22698,6 +26324,11 @@
         </is>
       </c>
       <c r="L130" s="21" t="inlineStr"/>
+      <c r="M130" s="16" t="inlineStr">
+        <is>
+          <t>Banco de trabajo con martillo, madera, clavos y repisa inferior.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="21" t="inlineStr">
@@ -22752,6 +26383,11 @@
         </is>
       </c>
       <c r="L131" s="21" t="inlineStr"/>
+      <c r="M131" s="16" t="inlineStr">
+        <is>
+          <t>Rueda zodiacal nocturna con anillos dorado/púrpura y estrella cyan.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="21" t="inlineStr">
@@ -22806,6 +26442,11 @@
         </is>
       </c>
       <c r="L132" s="21" t="inlineStr"/>
+      <c r="M132" s="16" t="inlineStr">
+        <is>
+          <t>Silla de espera de madera con respaldo de barrotes y cojín azul.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="21" t="inlineStr">
@@ -22860,6 +26501,11 @@
         </is>
       </c>
       <c r="L133" s="21" t="inlineStr"/>
+      <c r="M133" s="16" t="inlineStr">
+        <is>
+          <t>Flecha señalizadora de madera con puntos dorados y estaca.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="21" t="inlineStr">
@@ -22914,6 +26560,11 @@
         </is>
       </c>
       <c r="L134" s="21" t="inlineStr"/>
+      <c r="M134" s="16" t="inlineStr">
+        <is>
+          <t>Campanilla de mostrador dorada sobre base de madera.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="21" t="inlineStr">
@@ -22968,6 +26619,11 @@
         </is>
       </c>
       <c r="L135" s="21" t="inlineStr"/>
+      <c r="M135" s="16" t="inlineStr">
+        <is>
+          <t>Porta-tarjetas de madera con tarjetas crema.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="21" t="inlineStr">
@@ -23022,6 +26678,11 @@
         </is>
       </c>
       <c r="L136" s="21" t="inlineStr"/>
+      <c r="M136" s="16" t="inlineStr">
+        <is>
+          <t>Licencia enmarcada en madera con texto y sello rojo.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="21" t="inlineStr">
@@ -23076,6 +26737,11 @@
         </is>
       </c>
       <c r="L137" s="21" t="inlineStr"/>
+      <c r="M137" s="16" t="inlineStr">
+        <is>
+          <t>Registradora de hierro con pantallita cyan y teclas doradas.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="21" t="inlineStr">
@@ -23130,6 +26796,11 @@
         </is>
       </c>
       <c r="L138" s="21" t="inlineStr"/>
+      <c r="M138" s="16" t="inlineStr">
+        <is>
+          <t>Sillón acolchado rojo con respaldo redondeado, brazos oscuros y botón dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="21" t="inlineStr">
@@ -23184,6 +26855,11 @@
         </is>
       </c>
       <c r="L139" s="21" t="inlineStr"/>
+      <c r="M139" s="16" t="inlineStr">
+        <is>
+          <t>Silla de comedor de madera sencilla.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="21" t="inlineStr">
@@ -23238,6 +26914,11 @@
         </is>
       </c>
       <c r="L140" s="21" t="inlineStr"/>
+      <c r="M140" s="16" t="inlineStr">
+        <is>
+          <t>Libro de visitas rojo abierto con pluma dorada.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="21" t="inlineStr">
@@ -23292,6 +26973,11 @@
         </is>
       </c>
       <c r="L141" s="21" t="inlineStr"/>
+      <c r="M141" s="16" t="inlineStr">
+        <is>
+          <t>Pizarra de precios verde con patas, texto y precios dorados.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="21" t="inlineStr">
@@ -23346,6 +27032,11 @@
         </is>
       </c>
       <c r="L142" s="21" t="inlineStr"/>
+      <c r="M142" s="16" t="inlineStr">
+        <is>
+          <t>Mostrador de recepción largo con registro, campanita dorada y plantita.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="21" t="inlineStr">
@@ -23400,6 +27091,11 @@
         </is>
       </c>
       <c r="L143" s="21" t="inlineStr"/>
+      <c r="M143" s="16" t="inlineStr">
+        <is>
+          <t>Alfombra roja larga con borde dorado y textura.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="21" t="inlineStr">
@@ -23454,6 +27150,11 @@
         </is>
       </c>
       <c r="L144" s="21" t="inlineStr"/>
+      <c r="M144" s="16" t="inlineStr">
+        <is>
+          <t>Alfombra cyan con marco crema y medallón central.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="21" t="inlineStr">
@@ -23508,6 +27209,11 @@
         </is>
       </c>
       <c r="L145" s="21" t="inlineStr"/>
+      <c r="M145" s="16" t="inlineStr">
+        <is>
+          <t>Letrero colgante de madera con poción pintada y letras doradas.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="21" t="inlineStr">
@@ -23562,6 +27268,11 @@
         </is>
       </c>
       <c r="L146" s="21" t="inlineStr"/>
+      <c r="M146" s="16" t="inlineStr">
+        <is>
+          <t>Poste con dos flechas direccionales de madera y texto dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="21" t="inlineStr">
@@ -23616,6 +27327,11 @@
         </is>
       </c>
       <c r="L147" s="21" t="inlineStr"/>
+      <c r="M147" s="16" t="inlineStr">
+        <is>
+          <t>Alfombra verde con marco crema y flecos.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="21" t="inlineStr">
@@ -23670,19 +27386,24 @@
         </is>
       </c>
       <c r="L148" s="21" t="inlineStr"/>
+      <c r="M148" s="16" t="inlineStr">
+        <is>
+          <t>Felpudo dorado texturizado con 'HI' tejido.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -23696,6 +27417,7 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -23754,6 +27476,11 @@
           <t>Animación</t>
         </is>
       </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>Descripción Sprite</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -23807,6 +27534,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L2" s="16" t="inlineStr">
+        <is>
+          <t>Tierra marrón con textura moteada y parches claros.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -23860,6 +27592,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t>Piedras planas grises redondeadas sobre tierra oscura.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -23913,6 +27650,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>Tablones oscuros escalonados con veta.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -23966,6 +27708,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>Ladrillos terracota trabados con junta oscura.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -24019,6 +27766,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L6" s="16" t="inlineStr">
+        <is>
+          <t>Losas de mármol claro 2×2 con esquinas iluminadas.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -24072,6 +27824,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>Pasto verde con moteado orgánico de 3 tonos y bladecitos.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -24125,6 +27882,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>Pasto amarillento seco moteado.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -24178,6 +27940,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>Verde azulado musgoso con parches redondos.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -24231,6 +27998,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>Tierra violácea con motas lila brillantes.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -24284,6 +28056,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>Arena lila pálida con destellos cyan y blancos.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -24337,6 +28114,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>Piedra continua moteada gris.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -24394,6 +28176,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t>Tierra arada con surcos horizontales.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -24447,6 +28234,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t>Tierra arada oscurecida por riego.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -24500,6 +28292,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L15" s="16" t="inlineStr">
+        <is>
+          <t>Surcos con brotecitos verdes de 2 px.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -24553,6 +28350,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L16" s="16" t="inlineStr">
+        <is>
+          <t>Surcos con tallos verdes medianos.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -24606,6 +28408,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t>Plantas maduras con copa y destello dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -24659,6 +28466,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L18" s="16" t="inlineStr">
+        <is>
+          <t>Tallos amarillentos caídos.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -24712,6 +28524,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>Tablones medios escalonados.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -24765,6 +28582,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>Tablones claros escalonados con veta dorada.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -24818,6 +28640,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t>Baldosas grises de taller 2×2.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -24871,6 +28698,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L22" s="16" t="inlineStr">
+        <is>
+          <t>Piedra caliente grisácea con chispas naranja.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -24924,6 +28756,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L23" s="16" t="inlineStr">
+        <is>
+          <t>Baldosas verde alquímico con destellos verde/cyan.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -24977,6 +28814,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L24" s="16" t="inlineStr">
+        <is>
+          <t>Baldosas de mármol con vetas diagonales sutiles.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -25030,6 +28872,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t>Baldosas esmaltadas cyan brillante.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -25083,6 +28930,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L26" s="16" t="inlineStr">
+        <is>
+          <t>Alfombra roja con rombos.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -25136,6 +28988,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L27" s="16" t="inlineStr">
+        <is>
+          <t>Alfombra púrpura con rombos y textura de hilo.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -25189,6 +29046,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L28" s="16" t="inlineStr">
+        <is>
+          <t>Mosaico dorado de teselas pequeñas con brillos.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -25242,6 +29104,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L29" s="16" t="inlineStr">
+        <is>
+          <t>Baldosas negro violáceo con destellos púrpura.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -25299,6 +29166,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L30" s="16" t="inlineStr">
+        <is>
+          <t>Pasto con franja de tierra horizontal (transición).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -25356,6 +29228,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L31" s="16" t="inlineStr">
+        <is>
+          <t>Overlay cyan translúcido con marco (preview de construcción).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -25413,6 +29290,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L32" s="16" t="inlineStr">
+        <is>
+          <t>Overlay rojo translúcido con X (colocación inválida).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -25464,6 +29346,11 @@
       <c r="K33" s="16" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="L33" s="16" t="inlineStr">
+        <is>
+          <t>Piedra oscura con anillo rúnico cyan y 4 nodos.</t>
         </is>
       </c>
     </row>
@@ -25472,13 +29359,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -25492,6 +29379,7 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -25550,6 +29438,11 @@
           <t>Animación</t>
         </is>
       </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>Descripción Sprite</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -25603,6 +29496,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L2" s="16" t="inlineStr">
+        <is>
+          <t>Sillares de piedra clara.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -25656,6 +29554,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t>Tablones verticales claros.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -25709,6 +29612,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>Ladrillo crema cálido trabado.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -25762,6 +29670,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>Papel tapiz violeta con patrón de rombos lila y puntos dorados.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -25815,6 +29728,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L6" s="16" t="inlineStr">
+        <is>
+          <t>Sillares de piedra gris media.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -25868,6 +29786,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>Tablones verticales medios.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -25921,6 +29844,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>Ladrillo terracota trabado.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -25978,6 +29906,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>Esquina interior superior-izquierda (dos bandas).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -26035,6 +29968,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>Esquina interior superior-derecha.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -26092,6 +30030,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>Esquina interior inferior-izquierda.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -26149,6 +30092,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>Esquina interior inferior-derecha.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -26206,6 +30154,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t>Ladrillo interior con banda superior violeta oscura.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -26263,6 +30216,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t>Ladrillo interior con banda inferior violeta.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -26320,6 +30278,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L15" s="16" t="inlineStr">
+        <is>
+          <t>Ladrillo interior con banda izquierda violeta.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -26377,6 +30340,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L16" s="16" t="inlineStr">
+        <is>
+          <t>Ladrillo interior con banda derecha violeta.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -26430,6 +30398,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t>Puerta de madera en marco de piedra con pomo dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -26483,6 +30456,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L18" s="16" t="inlineStr">
+        <is>
+          <t>Marco con interior oscuro y hoja plegada al lado.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -26536,6 +30514,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>Puerta de hierro con remaches en las esquinas.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -26589,6 +30572,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>Puerta púrpura con runa lila central y chispas doradas.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -26646,6 +30634,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t>Puerta doble de madera con dos pomos dorados.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -26699,6 +30692,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L22" s="16" t="inlineStr">
+        <is>
+          <t>Ventana con cruz de madera y vidrio celeste sobre ladrillo.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -26752,6 +30750,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L23" s="16" t="inlineStr">
+        <is>
+          <t>Ventana con vidrio lila brillante y destellos dorados.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -26805,6 +30808,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L24" s="16" t="inlineStr">
+        <is>
+          <t>Ojo de buey redondo con cruz de madera.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -26862,6 +30870,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t>Columna de piedra gris.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -26919,6 +30932,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L26" s="16" t="inlineStr">
+        <is>
+          <t>Columna de mármol blanco con capitel y base.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -26976,6 +30994,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L27" s="16" t="inlineStr">
+        <is>
+          <t>Pilar púrpura con runas doradas y lila.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -27029,6 +31052,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L28" s="16" t="inlineStr">
+        <is>
+          <t>Cerca de madera de 2 travesaños con 3 postes sobre pasto.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -27082,6 +31110,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L29" s="16" t="inlineStr">
+        <is>
+          <t>Murete de piedra bajo sobre pasto.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -27135,6 +31168,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L30" s="16" t="inlineStr">
+        <is>
+          <t>Seto verde denso con florecitas rosas.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -27192,6 +31230,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L31" s="16" t="inlineStr">
+        <is>
+          <t>Arco de entrada de piedra con farolito dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -27249,1822 +31292,9 @@
           <t>No</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Tamaño</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Filename sugerido</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Color/Tema</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Función</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Notas</t>
-        </is>
-      </c>
-      <c r="J1" s="15" t="inlineStr">
-        <is>
-          <t>Animación</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>icon_coin</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Icono Moneda</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>HUD</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_coin.png</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Oro brillante</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Indica coins en HUD.</t>
-        </is>
-      </c>
-      <c r="H2" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="17" t="inlineStr">
-        <is>
-          <t>Spin 6f loop (rotación) · idle alterna estática + spin cada 4s</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>icon_reputation</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Icono Reputación</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>HUD</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_reputation.png</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Estrella dorada</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Indica reputación.</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>icon_inventory</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Icono Inventario</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>HUD</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_inventory.png</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Mochila marrón</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Botón inventario.</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>icon_build</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Icono Construir</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>HUD</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_build.png</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Martillo dorado</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Botón construir.</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>icon_research</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Icono Investigación</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>HUD</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_research.png</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Libro abierto azul</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Botón investigación.</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>icon_shop</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Icono Tienda</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>HUD</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_shop.png</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Bolsa con monedas</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Botón tienda.</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>icon_orders</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Icono Pedidos</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>HUD</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_orders.png</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Pergamino con marca</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Botón pedidos.</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>icon_settings</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Icono Ajustes</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>HUD</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_settings.png</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Engranaje plateado</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Botón ajustes.</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>icon_companion</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Icono Compañero</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>HUD</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_companion.png</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Silueta mago miniatura</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Botón modo compañero.</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>icon_pomodoro</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Icono Pomodoro</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Compañero</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_pomodoro.png</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Tomate rojo con tallo</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Widget pomodoro.</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>Spin 6f loop (rotación) · idle alterna estática + spin cada 4s</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>icon_notes</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Icono Notas</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Compañero</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_notes.png</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Pergamino con pluma</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Widget notas.</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>icon_todo</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Icono Tareas</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Compañero</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_todo.png</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Lista con check verde</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Widget to-do.</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>icon_ambient</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Icono Ambiente</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Compañero</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_ambient.png</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Onda de sonido azul</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Widget mezclador ambient.</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>icon_music</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Icono Música</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Compañero</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_music.png</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Nota musical dorada</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Widget reproductor.</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>icon_save</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Icono Guardar</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_save.png</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Disquete azul</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Botón guardar.</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>icon_load</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Icono Cargar</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_load.png</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Carpeta abierta dorada</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Botón cargar.</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>icon_close</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Icono Cerrar</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_close.png</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>X roja simple</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Cerrar panel.</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>icon_help</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Icono Ayuda</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_help.png</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Interrogación azul</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Tooltip ayuda.</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>icon_check</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Icono Check</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_check.png</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Tick verde</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Confirmar.</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>icon_alert</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Icono Alerta</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_alert.png</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Triángulo amarillo !</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Notificación.</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>icon_upgrade</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Icono Mejora</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>HUD</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_upgrade.png</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Flecha arriba dorada</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Botón mejorar.</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>icon_craft</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Icono Craftear</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>HUD</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/icon_craft.png</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Yunque pequeño</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Botón craftear.</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>cursor_default</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Cursor Default</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Cursor</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/cursor_default.png</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Flecha negra con borde</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Cursor normal.</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>cursor_build</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Cursor Construir</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Cursor</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/cursor_build.png</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Martillo pequeño</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Cursor modo construcción.</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>cursor_collect</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Cursor Recolectar</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Cursor</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/cursor_collect.png</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Mano abierta</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Hover sobre recurso.</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>frame_panel</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Frame Panel</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Frame</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>9-slice</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/frame_panel.png</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Madera con borde dorado</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>Marco de panel general.</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>9-slice</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>frame_popup</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Frame Popup</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Frame</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>9-slice</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/frame_popup.png</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Cristal con borde brillante</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Marco de popups.</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>9-slice</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>frame_tooltip</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Frame Tooltip</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Frame</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>9-slice</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/frame_tooltip.png</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Marrón oscuro con borde</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>Marco tooltips.</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>9-slice</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>button_default</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Botón Default</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>32×32 / 9-slice</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/button_default.png</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Madera con dorado</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Estado normal botón.</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>button_hover</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Botón Hover</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>32×32 / 9-slice</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/button_hover.png</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Madera más brillante</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>Estado hover.</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>button_pressed</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Botón Pressed</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>32×32 / 9-slice</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/button_pressed.png</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>Madera oscura hundida</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Estado pulsado.</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>badge_new</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Badge Nuevo</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Badge</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/badge_new.png</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Rojo con texto NEW</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>Notifica novedad.</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>badge_vip</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Badge VIP</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Badge</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/badge_vip.png</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>Dorado con corona</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Indica cliente VIP.</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>badge_event</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Badge Evento</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Badge</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>32×32</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/badge_event.png</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Púrpura con estrella</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>Indica evento activo.</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>progress_bar_fill</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Progress Bar Fill</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Bar</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>9-slice</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/progress_bar_fill.png</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>Verde con brillo</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>Relleno de barra.</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>progress_bar_bg</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Progress Bar Background</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Bar</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>9-slice</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>art/sprites/ui/progress_bar_bg.png</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Marrón oscuro hueco</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>Fondo de barra.</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Futuro</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="L32" s="16" t="inlineStr">
+        <is>
+          <t>Letrero de madera en poste con texto dorado sobre pasto.</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Maestro.xlsx
+++ b/Catalogo_Maestro.xlsx
@@ -15576,7 +15576,7 @@
       </c>
       <c r="L7" s="16" t="inlineStr">
         <is>
-          <t>Chibi del jugador: pelo castaño, delantal azul con hebilla dorada y capa púrpura a los lados. Grid 288×480 (idle 4 / walk 6).</t>
+          <t>Chibi del jugador (rediseño 'mago_completo', ideación SD jul 2026): boina púrpura ladeada con estrella dorada que destella, pelo lila hasta los hombros, túnica crema con cinturón y dobladillo dorados, capa púrpura y botas púrpura. Grid 288×480 (idle 4 / walk 6).</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Maestro.xlsx
+++ b/Catalogo_Maestro.xlsx
@@ -15576,7 +15576,7 @@
       </c>
       <c r="L7" s="16" t="inlineStr">
         <is>
-          <t>Chibi del jugador (rediseño 'mago_completo', ideación SD jul 2026): boina púrpura ladeada con estrella dorada que destella, pelo lila hasta los hombros, túnica crema con cinturón y dobladillo dorados, capa púrpura y botas púrpura. Grid 288×480 (idle 4 / walk 6).</t>
+          <t>Chibi del jugador (mago_completo HD, 48px nativos): boina púrpura ladeada con estrella dorada de 5 puntas que destella, pelo lila con mechones y brillos, ojos anime con iris lila, túnica crema con pliegues, cinturón y dobladillo dorados, capa púrpura con borde iluminado. Grid 288×480 (idle 4 / walk 6), celdas 48×48 SIN upscale (pitch 2 en pantalla).</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Maestro.xlsx
+++ b/Catalogo_Maestro.xlsx
@@ -15576,7 +15576,7 @@
       </c>
       <c r="L7" s="16" t="inlineStr">
         <is>
-          <t>Chibi del jugador (mago_completo HD, 48px nativos): boina púrpura ladeada con estrella dorada de 5 puntas que destella, pelo lila con mechones y brillos, ojos anime con iris lila, túnica crema con pliegues, cinturón y dobladillo dorados, capa púrpura con borde iluminado. Grid 288×480 (idle 4 / walk 6), celdas 48×48 SIN upscale (pitch 2 en pantalla).</t>
+          <t>Chibi del jugador (mago_completo, PRODUCCIÓN PixelLab jul 2026): boina púrpura con estrella dorada, pelo lila, túnica crema con cinturón dorado, capa púrpura con volumen y sombreado detallado nivel Sea of Stars. 48px nativos. Idle 4 = bob por código de la base aprobada; walk 6 = PixelLab animate-with-text (guidance 3, paleta arcana forzada). Base aprobada en sd-pixel/output/pixellab/protagonist/base48.png.</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Maestro.xlsx
+++ b/Catalogo_Maestro.xlsx
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -259,6 +259,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9969,7 +9972,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>Cada PNG conserva SIEMPRE sus dimensiones exactas actuales; las escenas usan AtlasTextures con regiones fijas.</t>
+          <t>Los PNG pueden cambiar de tamaño SOLO coordinadamente con su escena (regiones de AtlasTexture + colisión + escala en el mismo commit). Se BUSCA variedad de tamaños entre estaciones (jerarquía visual: forja 128 &gt; caldero/biblioteca 96 &gt; props menores 64) — no todo el mismo cuadro chico.</t>
         </is>
       </c>
     </row>
@@ -20700,9 +20703,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
-        <is>
-          <t>32×32 / 64×64</t>
+      <c r="F35" s="25" t="inlineStr">
+        <is>
+          <t>48×48 (escena ×2 → 96 px)</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
@@ -20721,15 +20724,15 @@
           <t>✅ Hecho</t>
         </is>
       </c>
-      <c r="K35" s="21" t="inlineStr">
-        <is>
-          <t>inicial</t>
+      <c r="K35" s="25" t="inlineStr">
+        <is>
+          <t>Jerarquía de tamaños: biblioteca alta (96px pantalla).</t>
         </is>
       </c>
       <c r="L35" s="21" t="inlineStr"/>
       <c r="M35" s="16" t="inlineStr">
         <is>
-          <t>Estantería de madera 32×32 con 3 filas de libros de colores.</t>
+          <t>Estantería alta PixelLab llena de libros de colores (derivada de rs_biblioteca 64).</t>
         </is>
       </c>
     </row>
@@ -20759,9 +20762,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="21" t="inlineStr">
-        <is>
-          <t>32×32 / 64×64</t>
+      <c r="F36" s="25" t="inlineStr">
+        <is>
+          <t>48×48 ×6 frames (escena ×2 → 96 px)</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -20780,15 +20783,15 @@
           <t>✅ Hecho</t>
         </is>
       </c>
-      <c r="K36" s="21" t="inlineStr">
-        <is>
-          <t>inicial</t>
+      <c r="K36" s="25" t="inlineStr">
+        <is>
+          <t>Jerarquía de tamaños: caldero mediano (96px pantalla).</t>
         </is>
       </c>
       <c r="L36" s="21" t="inlineStr"/>
       <c r="M36" s="16" t="inlineStr">
         <is>
-          <t>Caldero de hierro con brebaje verde burbujeante y llamas debajo (6 frames).</t>
+          <t>Caldero de hierro PixelLab con brebaje dorado burbujeante; 6 frames con burbujas/vapor por código. TAMAÑO MEDIO de la jerarquía.</t>
         </is>
       </c>
     </row>
@@ -20932,9 +20935,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F39" s="21" t="inlineStr">
-        <is>
-          <t>32×32 / 64×64</t>
+      <c r="F39" s="25" t="inlineStr">
+        <is>
+          <t>64×64 ×6 frames (escena ×2 → 128 px)</t>
         </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
@@ -20953,15 +20956,15 @@
           <t>✅ Hecho</t>
         </is>
       </c>
-      <c r="K39" s="21" t="inlineStr">
-        <is>
-          <t>inicial</t>
+      <c r="K39" s="25" t="inlineStr">
+        <is>
+          <t>Jerarquía de tamaños: forja grande (128px pantalla), domina la sala.</t>
         </is>
       </c>
       <c r="L39" s="21" t="inlineStr"/>
       <c r="M39" s="16" t="inlineStr">
         <is>
-          <t>Forja de piedra con boca incandescente que pulsa, chimenea y chispas (6 frames).</t>
+          <t>Gran horno de piedra PixelLab con fuego pulsante, chimenea y yunque; 6 frames con brasas/chispas por código. LA GRANDE de la sala, como la chimenea del mockup.</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Maestro.xlsx
+++ b/Catalogo_Maestro.xlsx
@@ -9922,7 +9922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9996,7 +9996,7 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>Púrpuras #3a2058 / #6e3aa0 / #9d6dff / #c89bff — color identidad de la tienda.</t>
+          <t>Púrpuras #3a2058/#6e3aa0/#9d6dff/#c89bff para magia/gemas/UI de campo. INTERIORES según mockup: piedra cálida gris-beige, maderas marrón miel a chocolate, dorados en detalles.</t>
         </is>
       </c>
     </row>
@@ -10124,12 +10124,36 @@
       <c r="B18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Referencia de ESTILO</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>art_reference/mockup_estilo.png — imagen norte del look final (sala de piedra+madera, densidad de props, UI madera/pergamino). TODO asset nuevo se genera con PixelLab bitforge usando un crop de esta imagen como style_image (style_strength ~55-70).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Jerarquía de tamaños</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Variedad deliberada (px pantalla, escena ×2): héroes 128×160+ (forja, biblioteca, alambique central), medianos 96 (caldero, mesas de trabajo), props 48-64, detalles 24-32. Nada de 'todo el mismo cuadro chico'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Generador PIL en ~/Proyectos/sd-pixel/cozy_all/ (un módulo por lote). Regenerar → copiar a godot/art/ → godot --headless --import → validar con movie mode.</t>
         </is>
@@ -20705,7 +20729,7 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>48×48 (escena ×2 → 96 px)</t>
+          <t>64×80 (escena ×2 → 128×160 px)</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
@@ -20726,13 +20750,13 @@
       </c>
       <c r="K35" s="25" t="inlineStr">
         <is>
-          <t>Jerarquía de tamaños: biblioteca alta (96px pantalla).</t>
+          <t>Jerarquía: héroe 128×160. Regenerar con bitforge + style_image del mockup.</t>
         </is>
       </c>
       <c r="L35" s="21" t="inlineStr"/>
       <c r="M35" s="16" t="inlineStr">
         <is>
-          <t>Estantería alta PixelLab llena de libros de colores (derivada de rs_biblioteca 64).</t>
+          <t>Gran librería de pared estilo mockup: alta, llena de libros, frascos y detalles; bitforge con mockup_estilo. Héroe de la sala.</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20961,7 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>64×64 ×6 frames (escena ×2 → 128 px)</t>
+          <t>64×80 ×6 frames (escena ×2 → 128×160 px)</t>
         </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
@@ -20958,13 +20982,13 @@
       </c>
       <c r="K39" s="25" t="inlineStr">
         <is>
-          <t>Jerarquía de tamaños: forja grande (128px pantalla), domina la sala.</t>
+          <t>Jerarquía: héroe 128×160. Regenerar con bitforge + style_image del mockup.</t>
         </is>
       </c>
       <c r="L39" s="21" t="inlineStr"/>
       <c r="M39" s="16" t="inlineStr">
         <is>
-          <t>Gran horno de piedra PixelLab con fuego pulsante, chimenea y yunque; 6 frames con brasas/chispas por código. LA GRANDE de la sala, como la chimenea del mockup.</t>
+          <t>Horno/chimenea de piedra ALTO estilo mockup, fuego pulsante, chimenea hasta arriba; bitforge con mockup_estilo. Héroe de la sala.</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Maestro.xlsx
+++ b/Catalogo_Maestro.xlsx
@@ -9922,7 +9922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10138,22 +10138,34 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
+          <t>Salas pintadas (diorama)</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Los fondos de sala NO son tilesets: se generan como ilustración con pixflux init_image = crops del mockup (strength 250, 3 paneles 320×368, media resolución + escala ×2 en escena = pitch 2 unificado). Limpieza con /inpaint: personajes horneados, letreros con texto sin sentido, restos de UI. Pipeline en cozy_all/diorama.py + output/pixellab/diorama/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
           <t>Jerarquía de tamaños</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Variedad deliberada (px pantalla, escena ×2): héroes 128×160+ (forja, biblioteca, alambique central), medianos 96 (caldero, mesas de trabajo), props 48-64, detalles 24-32. Nada de 'todo el mismo cuadro chico'.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Generador PIL en ~/Proyectos/sd-pixel/cozy_all/ (un módulo por lote). Regenerar → copiar a godot/art/ → godot --headless --import → validar con movie mode.</t>
         </is>

--- a/Catalogo_Maestro.xlsx
+++ b/Catalogo_Maestro.xlsx
@@ -10143,7 +10143,7 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Los fondos de sala NO son tilesets: se generan como ilustración con pixflux init_image = crops del mockup (strength 250, 3 paneles 320×368, media resolución + escala ×2 en escena = pitch 2 unificado). Limpieza con /inpaint: personajes horneados, letreros con texto sin sentido, restos de UI. Pipeline en cozy_all/diorama.py + output/pixellab/diorama/.</t>
+          <t>Los fondos de sala son SOLO estructura VACÍA: paredes de piedra + suelo de madera + puerta + ventanas. NADA de muebles/props horneados — el usuario decora con los props del juego. Compuesto por código (cozy_all/room_empty.py): piezas grandes PixelLab (floor/wall/door/window), pared irregular, suelo por recortes aleatorios (sin patrón tileset), viñeta cálida. 960×368 a escala ×2 = pitch 2 unificado.</t>
         </is>
       </c>
     </row>
@@ -20827,7 +20827,7 @@
       <c r="L36" s="21" t="inlineStr"/>
       <c r="M36" s="16" t="inlineStr">
         <is>
-          <t>Caldero de hierro PixelLab con brebaje dorado burbujeante; 6 frames con burbujas/vapor por código. TAMAÑO MEDIO de la jerarquía.</t>
+          <t>Caldero negro de hierro fundido redondo con asas, sobre base de troncos de madera, brebaje verde brillante burbujeante en la superficie; base PixelLab (ref del usuario), burbujas+vapor animados por código (6 frames). 48×48 → 96px pantalla.</t>
         </is>
       </c>
     </row>

--- a/Catalogo_Maestro.xlsx
+++ b/Catalogo_Maestro.xlsx
@@ -33,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,11 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00AA2255"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="16">
@@ -195,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -264,6 +269,7 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9922,7 +9928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9938,234 +9944,270 @@
       <c r="B1" s="16" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="B2" s="16" t="inlineStr"/>
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>★ ESTILO ACTUAL (jul 2026)</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>REINICIO a top-down cartoon estilo Zelda: The Minish Cap (art_reference/minish_ref.png). Descarta cozy-realista y salas pintadas.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
+          <t>Tiles Minish</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Tiles 16×16 pequeños, tileables/autotile, para decorar con TileMap en el editor. Generados por CÓDIGO (cozy_all/minish.py) = seamless perfecto. Contorno negro #21181b en objetos; suelos lineless. Cartoon NO realista: colores vivos, shading plano 2-3 tonos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Paleta Minish</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>ref/paleta_minish.png (28 colores): verdes #63ab3e/#8fc84f/#c8d45d, tierra #ab5130/#753027, arena/borde acantilado #feae70/#ffd196, cara acantilado #8e4d57, agua #4fa4b8/#92e8c0, piedra #a3a7c2, flores #f5ffe8/#ffd196/#a02b63. NO usar la paleta arcana vieja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="16" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
           <t>Regla</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Detalle</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Pitch unificado</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>1 píxel de arte = 2 píxeles de pantalla. Assets 64×64 y 40×40 se dibujan a media resolución y se escalan ×2 NEAREST; NPCs 32×48, decoraciones e items se dibujan nativos (sus escenas ya escalan ×2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dimensiones</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>Los PNG pueden cambiar de tamaño SOLO coordinadamente con su escena (regiones de AtlasTexture + colisión + escala en el mismo commit). Se BUSCA variedad de tamaños entre estaciones (jerarquía visual: forja 128 &gt; caldero/biblioteca 96 &gt; props menores 64) — no todo el mismo cuadro chico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Contorno</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>Contorno sticker de 1 px color #2b1b35 (violeta cálido, nunca negro puro), dibujado POR DEBAJO de los rellenos.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Paleta arcana</t>
+          <t>Pitch unificado</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>Púrpuras #3a2058/#6e3aa0/#9d6dff/#c89bff para magia/gemas/UI de campo. INTERIORES según mockup: piedra cálida gris-beige, maderas marrón miel a chocolate, dorados en detalles.</t>
+          <t>1 píxel de arte = 2 píxeles de pantalla. Assets 64×64 y 40×40 se dibujan a media resolución y se escalan ×2 NEAREST; NPCs 32×48, decoraciones e items se dibujan nativos (sus escenas ya escalan ×2).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Paleta dorada</t>
+          <t>Dimensiones</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>Dorados #855a14 / #d27d2c / #f0c060 (+#f8e0a0 highlight) — monedas, magia, madera cálida.</t>
+          <t>Los PNG pueden cambiar de tamaño SOLO coordinadamente con su escena (regiones de AtlasTexture + colisión + escala en el mismo commit). Se BUSCA variedad de tamaños entre estaciones (jerarquía visual: forja 128 &gt; caldero/biblioteca 96 &gt; props menores 64) — no todo el mismo cuadro chico.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Acentos</t>
+          <t>Contorno</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>Cyan #6dc2ca, rojo #d04648, azul #597dce, verde #6daa2c + tonos DB16. Piedra #757161/#8595a1, piel #d2aa99, madera #855a14/#a87848.</t>
+          <t>Contorno sticker de 1 px color #2b1b35 (violeta cálido, nunca negro puro), dibujado POR DEBAJO de los rellenos.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Caritas chibi</t>
+          <t>Paleta arcana</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Ojos 2×2 con brillo blanco arriba-izquierda, blush rosa #f0a0b0 a los lados, sonrisita de 2 px. Cabeza grande (~40% de la altura).</t>
+          <t>Púrpuras #3a2058/#6e3aa0/#9d6dff/#c89bff para magia/gemas/UI de campo. INTERIORES según mockup: piedra cálida gris-beige, maderas marrón miel a chocolate, dorados en detalles.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Animación idle</t>
+          <t>Paleta dorada</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>4 frames: bob vertical [0,1,1,0] + parpadeo en frame 3.</t>
+          <t>Dorados #855a14 / #d27d2c / #f0c060 (+#f8e0a0 highlight) — monedas, magia, madera cálida.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Animación walk</t>
+          <t>Acentos</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>6 frames: piernas alternas [-1,-1,0,0,0,0]/[0,0,0,-1,-1,0], bob [0,-1,0,0,-1,0], brazos en swing.</t>
+          <t>Cyan #6dc2ca, rojo #d04648, azul #597dce, verde #6daa2c + tonos DB16. Piedra #757161/#8595a1, piel #d2aa99, madera #855a14/#a87848.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Anim ambiente</t>
+          <t>Caritas chibi</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>Parcelas/caldero/forja: 6 frames horizontales, pulso suave + chispa/burbuja periódica.</t>
+          <t>Ojos 2×2 con brillo blanco arriba-izquierda, blush rosa #f0a0b0 a los lados, sonrisita de 2 px. Cabeza grande (~40% de la altura).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tiles</t>
+          <t>Animación idle</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Patrones seamless (aritmética modular); verificar repetición 2×2 antes de exportar.</t>
+          <t>4 frames: bob vertical [0,1,1,0] + parpadeo en frame 3.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Animación walk</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Madera con veta, piedra moteada (hash espacial, no lineal), vidrio translúcido con brillo diagonal 2 px, metal con highlight superior.</t>
+          <t>6 frames: piernas alternas [-1,-1,0,0,0,0]/[0,0,0,-1,-1,0], bob [0,-1,0,0,-1,0], brazos en swing.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Luz</t>
+          <t>Anim ambiente</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Fuente de luz arriba-izquierda: highlight en esa esquina, sombra propia abajo-derecha.</t>
+          <t>Parcelas/caldero/forja: 6 frames horizontales, pulso suave + chispa/burbuja periódica.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Tiles</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Patrones seamless (aritmética modular); verificar repetición 2×2 antes de exportar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Madera con veta, piedra moteada (hash espacial, no lineal), vidrio translúcido con brillo diagonal 2 px, metal con highlight superior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Fuente de luz arriba-izquierda: highlight en esa esquina, sombra propia abajo-derecha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Transparencias</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Espíritus/vidrio/overlays con alpha 120–230; sombras de contacto alpha ~90.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="16" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Referencia de ESTILO</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>art_reference/mockup_estilo.png — imagen norte del look final (sala de piedra+madera, densidad de props, UI madera/pergamino). TODO asset nuevo se genera con PixelLab bitforge usando un crop de esta imagen como style_image (style_strength ~55-70).</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Salas pintadas (diorama)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Los fondos de sala son SOLO estructura VACÍA: paredes de piedra + suelo de madera + puerta + ventanas. NADA de muebles/props horneados — el usuario decora con los props del juego. Compuesto por código (cozy_all/room_empty.py): piezas grandes PixelLab (floor/wall/door/window), pared irregular, suelo por recortes aleatorios (sin patrón tileset), viñeta cálida. 960×368 a escala ×2 = pitch 2 unificado.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Jerarquía de tamaños</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Variedad deliberada (px pantalla, escena ×2): héroes 128×160+ (forja, biblioteca, alambique central), medianos 96 (caldero, mesas de trabajo), props 48-64, detalles 24-32. Nada de 'todo el mismo cuadro chico'.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Generador PIL en ~/Proyectos/sd-pixel/cozy_all/ (un módulo por lote). Regenerar → copiar a godot/art/ → godot --headless --import → validar con movie mode.</t>
         </is>

--- a/Catalogo_Maestro.xlsx
+++ b/Catalogo_Maestro.xlsx
@@ -9671,7 +9671,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9715,7 +9714,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9759,7 +9757,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9803,7 +9800,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9847,7 +9843,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9891,7 +9886,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9935,7 +9929,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9979,7 +9972,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10023,7 +10015,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10067,7 +10058,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10111,7 +10101,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10155,7 +10144,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10199,7 +10187,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10243,7 +10230,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10287,7 +10273,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10331,7 +10316,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10375,7 +10359,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10419,7 +10402,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10463,7 +10445,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10507,7 +10488,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10551,7 +10531,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10595,7 +10574,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10639,7 +10617,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10683,7 +10660,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10727,7 +10703,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10771,7 +10746,6 @@
           <t>✅ Implementado</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26230,7 +26204,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -26240,7 +26214,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -26285,7 +26259,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -26295,7 +26269,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -26340,7 +26314,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -26350,7 +26324,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -26395,7 +26369,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -26405,7 +26379,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -26450,7 +26424,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -26460,7 +26434,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -26505,7 +26479,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -26515,7 +26489,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -26560,7 +26534,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -26570,7 +26544,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -26615,7 +26589,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -26625,7 +26599,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -26670,7 +26644,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -26680,7 +26654,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -26725,7 +26699,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -26735,7 +26709,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -26780,7 +26754,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -26790,7 +26764,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -26835,7 +26809,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -26845,7 +26819,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -26890,7 +26864,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -26900,7 +26874,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -26945,7 +26919,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -26955,7 +26929,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -27000,7 +26974,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -27010,7 +26984,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -27055,7 +27029,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -27065,7 +27039,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -27110,7 +27084,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -27120,7 +27094,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -27165,7 +27139,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -27175,7 +27149,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -27220,7 +27194,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -27230,7 +27204,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -27275,7 +27249,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -27285,7 +27259,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -27330,7 +27304,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -27340,7 +27314,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -27385,7 +27359,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -27395,7 +27369,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -27440,7 +27414,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -27450,7 +27424,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -27495,7 +27469,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -27505,7 +27479,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -27550,7 +27524,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -27560,7 +27534,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -27605,7 +27579,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -27615,7 +27589,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -27660,7 +27634,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -27670,7 +27644,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -27715,7 +27689,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -27725,7 +27699,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -27770,7 +27744,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -27780,7 +27754,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -27825,7 +27799,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -27835,7 +27809,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -27880,7 +27854,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -27890,7 +27864,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -27935,7 +27909,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -27945,7 +27919,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -27990,7 +27964,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -28000,7 +27974,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -28045,7 +28019,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -28055,7 +28029,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -28100,7 +28074,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -28110,7 +28084,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -28155,7 +28129,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -28165,7 +28139,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -28210,7 +28184,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -28220,7 +28194,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -28265,7 +28239,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -28275,7 +28249,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -28320,7 +28294,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -28330,7 +28304,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -28375,7 +28349,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -28385,7 +28359,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -28423,7 +28397,6 @@
           <t>items/amuleto_fenix.png</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>Joya que arde con el fuego primordial de un elemental.</t>
@@ -28431,7 +28404,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -28441,7 +28414,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -28449,7 +28422,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -28480,7 +28452,6 @@
           <t>items/cetro_tormenta.png</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>Vara que comanda el poder de los cielos.</t>
@@ -28488,7 +28459,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -28498,7 +28469,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -28506,7 +28477,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -28537,7 +28507,6 @@
           <t>items/corona_escarcha.png</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>Diadema de hielo eterno que no se derrite.</t>
@@ -28545,7 +28514,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -28555,7 +28524,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -28563,7 +28532,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -28594,7 +28562,6 @@
           <t>items/orbe_fusion.png</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>Esfera donde convergen las fuerzas del cosmos.</t>
@@ -28602,7 +28569,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -28612,7 +28579,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -28620,7 +28587,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -28651,7 +28617,6 @@
           <t>items/polvo_constelaciones.png</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>Restos pulverizados de constelaciones olvidadas.</t>
@@ -28659,7 +28624,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>⏳ FALTA SPRITE</t>
+          <t>✅ Obtainable</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -28669,7 +28634,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>static</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -28677,7 +28642,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
